--- a/artfynd/A 50406-2025 artfynd.xlsx
+++ b/artfynd/A 50406-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129240173</v>
       </c>
       <c r="B2" t="n">
-        <v>79037</v>
+        <v>79039</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129240172</v>
       </c>
       <c r="B3" t="n">
-        <v>79037</v>
+        <v>79039</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129240149</v>
       </c>
       <c r="B4" t="n">
-        <v>91531</v>
+        <v>91533</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>129240151</v>
       </c>
       <c r="B5" t="n">
-        <v>91480</v>
+        <v>91482</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>129240155</v>
       </c>
       <c r="B6" t="n">
-        <v>91986</v>
+        <v>91988</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 50406-2025 artfynd.xlsx
+++ b/artfynd/A 50406-2025 artfynd.xlsx
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129240149</v>
+        <v>129240151</v>
       </c>
       <c r="B4" t="n">
-        <v>91533</v>
+        <v>91489</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>112</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>789296</v>
+        <v>789340</v>
       </c>
       <c r="R4" t="n">
-        <v>7151183</v>
+        <v>7151270</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129240151</v>
+        <v>129240149</v>
       </c>
       <c r="B5" t="n">
-        <v>91482</v>
+        <v>91540</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>112</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>789340</v>
+        <v>789296</v>
       </c>
       <c r="R5" t="n">
-        <v>7151270</v>
+        <v>7151183</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,7 +1066,7 @@
         <v>129240155</v>
       </c>
       <c r="B6" t="n">
-        <v>91988</v>
+        <v>91995</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 50406-2025 artfynd.xlsx
+++ b/artfynd/A 50406-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129240173</v>
       </c>
       <c r="B2" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129240172</v>
       </c>
       <c r="B3" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129240151</v>
+        <v>129240149</v>
       </c>
       <c r="B4" t="n">
-        <v>91489</v>
+        <v>91542</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>112</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>789340</v>
+        <v>789296</v>
       </c>
       <c r="R4" t="n">
-        <v>7151270</v>
+        <v>7151183</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129240149</v>
+        <v>129240151</v>
       </c>
       <c r="B5" t="n">
-        <v>91540</v>
+        <v>91491</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>112</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>789296</v>
+        <v>789340</v>
       </c>
       <c r="R5" t="n">
-        <v>7151183</v>
+        <v>7151270</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,7 +1066,7 @@
         <v>129240155</v>
       </c>
       <c r="B6" t="n">
-        <v>91995</v>
+        <v>91997</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 50406-2025 artfynd.xlsx
+++ b/artfynd/A 50406-2025 artfynd.xlsx
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129240149</v>
+        <v>129240151</v>
       </c>
       <c r="B4" t="n">
-        <v>91542</v>
+        <v>91491</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>112</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>789296</v>
+        <v>789340</v>
       </c>
       <c r="R4" t="n">
-        <v>7151183</v>
+        <v>7151270</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129240151</v>
+        <v>129240149</v>
       </c>
       <c r="B5" t="n">
-        <v>91491</v>
+        <v>91540</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>112</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>789340</v>
+        <v>789296</v>
       </c>
       <c r="R5" t="n">
-        <v>7151270</v>
+        <v>7151183</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,7 +1066,7 @@
         <v>129240155</v>
       </c>
       <c r="B6" t="n">
-        <v>91997</v>
+        <v>91992</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1083,12 +1083,12 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>

--- a/artfynd/A 50406-2025 artfynd.xlsx
+++ b/artfynd/A 50406-2025 artfynd.xlsx
@@ -1066,7 +1066,7 @@
         <v>129240155</v>
       </c>
       <c r="B6" t="n">
-        <v>91992</v>
+        <v>91993</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 50406-2025 artfynd.xlsx
+++ b/artfynd/A 50406-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129240173</v>
       </c>
       <c r="B2" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129240172</v>
       </c>
       <c r="B3" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129240151</v>
       </c>
       <c r="B4" t="n">
-        <v>91491</v>
+        <v>91494</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>129240149</v>
       </c>
       <c r="B5" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>129240155</v>
       </c>
       <c r="B6" t="n">
-        <v>91993</v>
+        <v>91996</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 50406-2025 artfynd.xlsx
+++ b/artfynd/A 50406-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129240173</v>
       </c>
       <c r="B2" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129240172</v>
       </c>
       <c r="B3" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129240151</v>
       </c>
       <c r="B4" t="n">
-        <v>91494</v>
+        <v>91496</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>129240149</v>
       </c>
       <c r="B5" t="n">
-        <v>91543</v>
+        <v>91545</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>129240155</v>
       </c>
       <c r="B6" t="n">
-        <v>91996</v>
+        <v>91998</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 50406-2025 artfynd.xlsx
+++ b/artfynd/A 50406-2025 artfynd.xlsx
@@ -872,7 +872,7 @@
         <v>129240151</v>
       </c>
       <c r="B4" t="n">
-        <v>91496</v>
+        <v>91500</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>129240149</v>
       </c>
       <c r="B5" t="n">
-        <v>91545</v>
+        <v>91549</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>129240155</v>
       </c>
       <c r="B6" t="n">
-        <v>91998</v>
+        <v>92002</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 50406-2025 artfynd.xlsx
+++ b/artfynd/A 50406-2025 artfynd.xlsx
@@ -872,7 +872,7 @@
         <v>129240151</v>
       </c>
       <c r="B4" t="n">
-        <v>91500</v>
+        <v>91501</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>129240149</v>
       </c>
       <c r="B5" t="n">
-        <v>91549</v>
+        <v>91550</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>129240155</v>
       </c>
       <c r="B6" t="n">
-        <v>92002</v>
+        <v>92003</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 50406-2025 artfynd.xlsx
+++ b/artfynd/A 50406-2025 artfynd.xlsx
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129240151</v>
+        <v>129240149</v>
       </c>
       <c r="B4" t="n">
-        <v>91501</v>
+        <v>91550</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>112</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>789340</v>
+        <v>789296</v>
       </c>
       <c r="R4" t="n">
-        <v>7151270</v>
+        <v>7151183</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129240149</v>
+        <v>129240151</v>
       </c>
       <c r="B5" t="n">
-        <v>91550</v>
+        <v>91501</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>112</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>789296</v>
+        <v>789340</v>
       </c>
       <c r="R5" t="n">
-        <v>7151183</v>
+        <v>7151270</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 50406-2025 artfynd.xlsx
+++ b/artfynd/A 50406-2025 artfynd.xlsx
@@ -872,7 +872,7 @@
         <v>129240149</v>
       </c>
       <c r="B4" t="n">
-        <v>91550</v>
+        <v>91553</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>129240151</v>
       </c>
       <c r="B5" t="n">
-        <v>91501</v>
+        <v>91504</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>129240155</v>
       </c>
       <c r="B6" t="n">
-        <v>92003</v>
+        <v>92006</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 50406-2025 artfynd.xlsx
+++ b/artfynd/A 50406-2025 artfynd.xlsx
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129240149</v>
+        <v>129240151</v>
       </c>
       <c r="B4" t="n">
-        <v>91553</v>
+        <v>91504</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>112</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>789296</v>
+        <v>789340</v>
       </c>
       <c r="R4" t="n">
-        <v>7151183</v>
+        <v>7151270</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129240151</v>
+        <v>129240149</v>
       </c>
       <c r="B5" t="n">
-        <v>91504</v>
+        <v>91553</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>112</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>789340</v>
+        <v>789296</v>
       </c>
       <c r="R5" t="n">
-        <v>7151270</v>
+        <v>7151183</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 50406-2025 artfynd.xlsx
+++ b/artfynd/A 50406-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129240173</v>
       </c>
       <c r="B2" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129240172</v>
       </c>
       <c r="B3" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129240151</v>
       </c>
       <c r="B4" t="n">
-        <v>91504</v>
+        <v>91532</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>129240149</v>
       </c>
       <c r="B5" t="n">
-        <v>91553</v>
+        <v>91581</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>129240155</v>
       </c>
       <c r="B6" t="n">
-        <v>92006</v>
+        <v>92034</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 50406-2025 artfynd.xlsx
+++ b/artfynd/A 50406-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>129240173</v>
       </c>
       <c r="B2" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129240172</v>
       </c>
       <c r="B3" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129240151</v>
+        <v>129240149</v>
       </c>
       <c r="B4" t="n">
-        <v>91532</v>
+        <v>91587</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>112</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>789340</v>
+        <v>789296</v>
       </c>
       <c r="R4" t="n">
-        <v>7151270</v>
+        <v>7151183</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129240149</v>
+        <v>129240151</v>
       </c>
       <c r="B5" t="n">
-        <v>91581</v>
+        <v>91538</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>112</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>789296</v>
+        <v>789340</v>
       </c>
       <c r="R5" t="n">
-        <v>7151183</v>
+        <v>7151270</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,7 +1066,7 @@
         <v>129240155</v>
       </c>
       <c r="B6" t="n">
-        <v>92034</v>
+        <v>92040</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1157,6 +1157,3969 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>129742487</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79075</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Öster om Boströmberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>789354</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7151266</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Robertsfors</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Nysätra</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>129745363</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57732</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Öster om Boströmberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>789241</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7151185</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Robertsfors</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Nysätra</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>på nära håll</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>129745889</v>
+      </c>
+      <c r="B9" t="n">
+        <v>82910</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Öster om Boströmberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>789222</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7151172</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Robertsfors</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Nysätra</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>129743137</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57735</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Öster om Boströmberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>789220</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7151136</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Robertsfors</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Nysätra</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>färska ringhack som utgörs av små punkthack på en gran</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>129742539</v>
+      </c>
+      <c r="B11" t="n">
+        <v>91587</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Öster om Boströmberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>789298</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7151197</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Robertsfors</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Nysätra</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>på samma låga som rynkskinn</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>129745347</v>
+      </c>
+      <c r="B12" t="n">
+        <v>79075</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Öster om Boströmberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>789248</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7151191</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Robertsfors</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Nysätra</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>på stammen av en tall</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>129745328</v>
+      </c>
+      <c r="B13" t="n">
+        <v>79075</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Öster om Boströmberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>789227</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7151210</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Robertsfors</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Nysätra</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>129745950</v>
+      </c>
+      <c r="B14" t="n">
+        <v>82910</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Öster om Boströmberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>789199</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7151153</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Robertsfors</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Nysätra</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>129742521</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57735</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Öster om Boströmberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>789331</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7151248</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Robertsfors</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Nysätra</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>129743913</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57735</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Öster om Boströmberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>789283</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7151180</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Robertsfors</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Nysätra</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>ringhack på gammal gran</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>129742406</v>
+      </c>
+      <c r="B17" t="n">
+        <v>79075</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Öster om Boströmberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>789267</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7151238</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Robertsfors</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Nysätra</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>129746089</v>
+      </c>
+      <c r="B18" t="n">
+        <v>82910</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Öster om Boströmberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>789203</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7151242</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Robertsfors</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Nysätra</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>129745466</v>
+      </c>
+      <c r="B19" t="n">
+        <v>57732</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Öster om Boströmberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>789212</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7151164</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Robertsfors</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Nysätra</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>bohål i gran</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>129742963</v>
+      </c>
+      <c r="B20" t="n">
+        <v>5177</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Öster om Boströmberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>789174</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7151114</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Robertsfors</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Nysätra</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>gnagspår i död gran</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>129745993</v>
+      </c>
+      <c r="B21" t="n">
+        <v>79075</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Öster om Boströmberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>789196</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7151151</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Robertsfors</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Nysätra</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>ca 70cm lång bål!</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>129742631</v>
+      </c>
+      <c r="B22" t="n">
+        <v>91538</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>112</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Stjärntagging</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Asterodon ferruginosus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Pat.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Öster om Boströmberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>789289</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7151198</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Robertsfors</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Nysätra</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>129745192</v>
+      </c>
+      <c r="B23" t="n">
+        <v>79075</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Öster om Boströmberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>789210</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7151242</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Robertsfors</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Nysätra</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>129742557</v>
+      </c>
+      <c r="B24" t="n">
+        <v>92040</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Öster om Boströmberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>789298</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7151197</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Robertsfors</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Nysätra</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>på samma granlåga som ullticka</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>129745532</v>
+      </c>
+      <c r="B25" t="n">
+        <v>57732</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Öster om Boströmberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>789215</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7151159</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Robertsfors</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Nysätra</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>hack i låga</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>129744135</v>
+      </c>
+      <c r="B26" t="n">
+        <v>57735</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Öster om Boströmberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>789284</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7151167</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Robertsfors</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Nysätra</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>äldre ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>129745551</v>
+      </c>
+      <c r="B27" t="n">
+        <v>79075</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Öster om Boströmberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>789219</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7151168</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Robertsfors</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Nysätra</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>129745563</v>
+      </c>
+      <c r="B28" t="n">
+        <v>91551</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Öster om Boströmberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>789198</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7151158</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Robertsfors</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Nysätra</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>129742620</v>
+      </c>
+      <c r="B29" t="n">
+        <v>91551</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Öster om Boströmberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>789294</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7151188</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Robertsfors</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Nysätra</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>129745383</v>
+      </c>
+      <c r="B30" t="n">
+        <v>79075</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Öster om Boströmberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>789239</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7151169</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Robertsfors</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Nysätra</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>fertil</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>129745427</v>
+      </c>
+      <c r="B31" t="n">
+        <v>79075</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Öster om Boströmberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>789221</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7151169</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Robertsfors</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Nysätra</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>129742300</v>
+      </c>
+      <c r="B32" t="n">
+        <v>57732</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Öster om Boströmberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>789197</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7151175</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Robertsfors</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Nysätra</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>hål i tall</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>129745155</v>
+      </c>
+      <c r="B33" t="n">
+        <v>79075</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Öster om Boströmberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>789288</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7151234</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Robertsfors</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Nysätra</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="inlineStr"/>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>129742254</v>
+      </c>
+      <c r="B34" t="n">
+        <v>79107</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>185</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Öster om Boströmberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>789175</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7151217</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Robertsfors</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Nysätra</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>129742429</v>
+      </c>
+      <c r="B35" t="n">
+        <v>79075</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Öster om Boströmberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>789351</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7151276</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Robertsfors</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Nysätra</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>129744558</v>
+      </c>
+      <c r="B36" t="n">
+        <v>91587</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Öster om Boströmberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>789368</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7151214</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Robertsfors</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Nysätra</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>129742261</v>
+      </c>
+      <c r="B37" t="n">
+        <v>57735</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Öster om Boströmberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>789192</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7151225</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Robertsfors</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Nysätra</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>barksprätt på gammal gran</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>129742447</v>
+      </c>
+      <c r="B38" t="n">
+        <v>79075</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Öster om Boströmberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>789380</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7151245</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Robertsfors</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Nysätra</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>på stammen av en tall</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="inlineStr"/>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>129745159</v>
+      </c>
+      <c r="B39" t="n">
+        <v>79075</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Öster om Boströmberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>789266</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7151263</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Robertsfors</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Nysätra</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF39" t="inlineStr"/>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>129745946</v>
+      </c>
+      <c r="B40" t="n">
+        <v>82910</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Öster om Boströmberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>789208</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7151157</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Robertsfors</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Nysätra</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF40" t="inlineStr"/>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>129745167</v>
+      </c>
+      <c r="B41" t="n">
+        <v>79075</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Öster om Boströmberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>789233</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7151272</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Robertsfors</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Nysätra</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF41" t="inlineStr"/>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>129742518</v>
+      </c>
+      <c r="B42" t="n">
+        <v>91551</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Öster om Boströmberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>789345</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7151261</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Robertsfors</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Nysätra</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF42" t="inlineStr"/>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>129742516</v>
+      </c>
+      <c r="B43" t="n">
+        <v>79075</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Öster om Boströmberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>789348</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7151255</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Robertsfors</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Nysätra</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF43" t="inlineStr"/>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 50406-2025 artfynd.xlsx
+++ b/artfynd/A 50406-2025 artfynd.xlsx
@@ -1163,7 +1163,7 @@
         <v>129742487</v>
       </c>
       <c r="B7" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1265,10 +1265,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129745363</v>
+        <v>129745889</v>
       </c>
       <c r="B8" t="n">
-        <v>57732</v>
+        <v>82911</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1276,31 +1276,30 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>1312</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1308,10 +1307,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>789241</v>
+        <v>789222</v>
       </c>
       <c r="R8" t="n">
-        <v>7151185</v>
+        <v>7151172</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1346,17 +1345,13 @@
           <t>2025-10-28</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>på nära håll</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1375,10 +1370,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129745889</v>
+        <v>129745363</v>
       </c>
       <c r="B9" t="n">
-        <v>82910</v>
+        <v>57733</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1386,30 +1381,31 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1312</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1417,10 +1413,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>789222</v>
+        <v>789241</v>
       </c>
       <c r="R9" t="n">
-        <v>7151172</v>
+        <v>7151185</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1455,13 +1451,17 @@
           <t>2025-10-28</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>på nära håll</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1483,7 +1483,7 @@
         <v>129743137</v>
       </c>
       <c r="B10" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         <v>129742539</v>
       </c>
       <c r="B11" t="n">
-        <v>91587</v>
+        <v>91588</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1700,10 +1700,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129745347</v>
+        <v>129745950</v>
       </c>
       <c r="B12" t="n">
-        <v>79075</v>
+        <v>82911</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1711,27 +1711,27 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1742,10 +1742,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>789248</v>
+        <v>789199</v>
       </c>
       <c r="R12" t="n">
-        <v>7151191</v>
+        <v>7151153</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1778,11 +1778,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-28</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>på stammen av en tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1810,10 +1805,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129745328</v>
+        <v>129745347</v>
       </c>
       <c r="B13" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1852,10 +1847,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>789227</v>
+        <v>789248</v>
       </c>
       <c r="R13" t="n">
-        <v>7151210</v>
+        <v>7151191</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1888,6 +1883,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>på stammen av en tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1915,10 +1915,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129745950</v>
+        <v>129745328</v>
       </c>
       <c r="B14" t="n">
-        <v>82910</v>
+        <v>79076</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1926,27 +1926,27 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -1957,10 +1957,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>789199</v>
+        <v>789227</v>
       </c>
       <c r="R14" t="n">
-        <v>7151153</v>
+        <v>7151210</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2020,10 +2020,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129742521</v>
+        <v>129743913</v>
       </c>
       <c r="B15" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2053,7 +2053,7 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -2063,10 +2063,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>789331</v>
+        <v>789283</v>
       </c>
       <c r="R15" t="n">
-        <v>7151248</v>
+        <v>7151180</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2103,7 +2103,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>ringhack på tall</t>
+          <t>ringhack på gammal gran</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2130,10 +2130,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129743913</v>
+        <v>129742521</v>
       </c>
       <c r="B16" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2163,7 +2163,7 @@
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -2173,10 +2173,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>789283</v>
+        <v>789331</v>
       </c>
       <c r="R16" t="n">
-        <v>7151180</v>
+        <v>7151248</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2213,7 +2213,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>ringhack på gammal gran</t>
+          <t>ringhack på tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2243,7 +2243,7 @@
         <v>129742406</v>
       </c>
       <c r="B17" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
         <v>129746089</v>
       </c>
       <c r="B18" t="n">
-        <v>82910</v>
+        <v>82911</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2453,7 +2453,7 @@
         <v>129745466</v>
       </c>
       <c r="B19" t="n">
-        <v>57732</v>
+        <v>57733</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2675,7 +2675,7 @@
         <v>129745993</v>
       </c>
       <c r="B21" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2785,7 +2785,7 @@
         <v>129742631</v>
       </c>
       <c r="B22" t="n">
-        <v>91538</v>
+        <v>91539</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2890,7 +2890,7 @@
         <v>129745192</v>
       </c>
       <c r="B23" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2995,7 +2995,7 @@
         <v>129742557</v>
       </c>
       <c r="B24" t="n">
-        <v>92040</v>
+        <v>92041</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3101,7 +3101,7 @@
         <v>129745532</v>
       </c>
       <c r="B25" t="n">
-        <v>57732</v>
+        <v>57733</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3208,42 +3208,41 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129744135</v>
+        <v>129745563</v>
       </c>
       <c r="B26" t="n">
-        <v>57735</v>
+        <v>91552</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3251,10 +3250,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>789284</v>
+        <v>789198</v>
       </c>
       <c r="R26" t="n">
-        <v>7151167</v>
+        <v>7151158</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3289,17 +3288,13 @@
           <t>2025-10-28</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>äldre ringhack på gran</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3318,10 +3313,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129745551</v>
+        <v>129744135</v>
       </c>
       <c r="B27" t="n">
-        <v>79075</v>
+        <v>57736</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3329,30 +3324,31 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3360,10 +3356,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>789219</v>
+        <v>789284</v>
       </c>
       <c r="R27" t="n">
-        <v>7151168</v>
+        <v>7151167</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3398,13 +3394,17 @@
           <t>2025-10-28</t>
         </is>
       </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>äldre ringhack på gran</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3423,38 +3423,38 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129745563</v>
+        <v>129745551</v>
       </c>
       <c r="B28" t="n">
-        <v>91551</v>
+        <v>79076</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
@@ -3465,10 +3465,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>789198</v>
+        <v>789219</v>
       </c>
       <c r="R28" t="n">
-        <v>7151158</v>
+        <v>7151168</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3528,41 +3528,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129742620</v>
+        <v>129745383</v>
       </c>
       <c r="B29" t="n">
-        <v>91551</v>
+        <v>79076</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr"/>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3570,10 +3574,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>789294</v>
+        <v>789239</v>
       </c>
       <c r="R29" t="n">
-        <v>7151188</v>
+        <v>7151169</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3606,6 +3610,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>fertil</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3633,10 +3642,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129745383</v>
+        <v>129745427</v>
       </c>
       <c r="B30" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3667,11 +3676,7 @@
           <t>bålar</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3679,7 +3684,7 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>789239</v>
+        <v>789221</v>
       </c>
       <c r="R30" t="n">
         <v>7151169</v>
@@ -3715,11 +3720,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-10-28</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>fertil</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3747,38 +3747,38 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129745427</v>
+        <v>129742620</v>
       </c>
       <c r="B31" t="n">
-        <v>79075</v>
+        <v>91552</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
@@ -3789,10 +3789,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>789221</v>
+        <v>789294</v>
       </c>
       <c r="R31" t="n">
-        <v>7151169</v>
+        <v>7151188</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3852,10 +3852,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129742300</v>
+        <v>129745155</v>
       </c>
       <c r="B32" t="n">
-        <v>57732</v>
+        <v>79076</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3863,31 +3863,30 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -3895,10 +3894,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>789197</v>
+        <v>789288</v>
       </c>
       <c r="R32" t="n">
-        <v>7151175</v>
+        <v>7151234</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3933,17 +3932,13 @@
           <t>2025-10-28</t>
         </is>
       </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>hål i tall</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -3962,10 +3957,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129745155</v>
+        <v>129742300</v>
       </c>
       <c r="B33" t="n">
-        <v>79075</v>
+        <v>57733</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3973,30 +3968,31 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4004,10 +4000,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>789288</v>
+        <v>789197</v>
       </c>
       <c r="R33" t="n">
-        <v>7151234</v>
+        <v>7151175</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4042,13 +4038,17 @@
           <t>2025-10-28</t>
         </is>
       </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>hål i tall</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4070,7 +4070,7 @@
         <v>129742254</v>
       </c>
       <c r="B34" t="n">
-        <v>79107</v>
+        <v>79108</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4175,7 +4175,7 @@
         <v>129742429</v>
       </c>
       <c r="B35" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4277,10 +4277,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129744558</v>
+        <v>129742261</v>
       </c>
       <c r="B36" t="n">
-        <v>91587</v>
+        <v>57736</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4288,30 +4288,27 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4319,10 +4316,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>789368</v>
+        <v>789192</v>
       </c>
       <c r="R36" t="n">
-        <v>7151214</v>
+        <v>7151225</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4357,13 +4354,17 @@
           <t>2025-10-28</t>
         </is>
       </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>barksprätt på gammal gran</t>
+        </is>
+      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4382,10 +4383,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129742261</v>
+        <v>129744558</v>
       </c>
       <c r="B37" t="n">
-        <v>57735</v>
+        <v>91588</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4393,27 +4394,30 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4421,10 +4425,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>789192</v>
+        <v>789368</v>
       </c>
       <c r="R37" t="n">
-        <v>7151225</v>
+        <v>7151214</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4459,17 +4463,13 @@
           <t>2025-10-28</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>barksprätt på gammal gran</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4491,7 +4491,7 @@
         <v>129742447</v>
       </c>
       <c r="B38" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4601,7 +4601,7 @@
         <v>129745159</v>
       </c>
       <c r="B39" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4703,10 +4703,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129745946</v>
+        <v>129745167</v>
       </c>
       <c r="B40" t="n">
-        <v>82910</v>
+        <v>79076</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4714,27 +4714,27 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
@@ -4745,10 +4745,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>789208</v>
+        <v>789233</v>
       </c>
       <c r="R40" t="n">
-        <v>7151157</v>
+        <v>7151272</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4808,10 +4808,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129745167</v>
+        <v>129745946</v>
       </c>
       <c r="B41" t="n">
-        <v>79075</v>
+        <v>82911</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4819,27 +4819,27 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
@@ -4850,10 +4850,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>789233</v>
+        <v>789208</v>
       </c>
       <c r="R41" t="n">
-        <v>7151272</v>
+        <v>7151157</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4916,7 +4916,7 @@
         <v>129742518</v>
       </c>
       <c r="B42" t="n">
-        <v>91551</v>
+        <v>91552</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5021,7 +5021,7 @@
         <v>129742516</v>
       </c>
       <c r="B43" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/A 50406-2025 artfynd.xlsx
+++ b/artfynd/A 50406-2025 artfynd.xlsx
@@ -3528,45 +3528,41 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129745383</v>
+        <v>129742620</v>
       </c>
       <c r="B29" t="n">
-        <v>79076</v>
+        <v>91552</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3574,10 +3570,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>789239</v>
+        <v>789294</v>
       </c>
       <c r="R29" t="n">
-        <v>7151169</v>
+        <v>7151188</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3610,11 +3606,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-10-28</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>fertil</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3642,7 +3633,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129745427</v>
+        <v>129745383</v>
       </c>
       <c r="B30" t="n">
         <v>79076</v>
@@ -3676,7 +3667,11 @@
           <t>bålar</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3684,7 +3679,7 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>789221</v>
+        <v>789239</v>
       </c>
       <c r="R30" t="n">
         <v>7151169</v>
@@ -3720,6 +3715,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>fertil</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3747,38 +3747,38 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129742620</v>
+        <v>129745427</v>
       </c>
       <c r="B31" t="n">
-        <v>91552</v>
+        <v>79076</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
@@ -3789,10 +3789,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>789294</v>
+        <v>789221</v>
       </c>
       <c r="R31" t="n">
-        <v>7151188</v>
+        <v>7151169</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3852,10 +3852,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129745155</v>
+        <v>129742300</v>
       </c>
       <c r="B32" t="n">
-        <v>79076</v>
+        <v>57733</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3863,30 +3863,31 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -3894,10 +3895,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>789288</v>
+        <v>789197</v>
       </c>
       <c r="R32" t="n">
-        <v>7151234</v>
+        <v>7151175</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3932,13 +3933,17 @@
           <t>2025-10-28</t>
         </is>
       </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>hål i tall</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -3957,10 +3962,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129742300</v>
+        <v>129745155</v>
       </c>
       <c r="B33" t="n">
-        <v>57733</v>
+        <v>79076</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3968,31 +3973,30 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4000,10 +4004,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>789197</v>
+        <v>789288</v>
       </c>
       <c r="R33" t="n">
-        <v>7151175</v>
+        <v>7151234</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4038,17 +4042,13 @@
           <t>2025-10-28</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>hål i tall</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4172,10 +4172,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129742429</v>
+        <v>129742261</v>
       </c>
       <c r="B35" t="n">
-        <v>79076</v>
+        <v>57736</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4183,30 +4183,27 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4214,10 +4211,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>789351</v>
+        <v>789192</v>
       </c>
       <c r="R35" t="n">
-        <v>7151276</v>
+        <v>7151225</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4252,13 +4249,17 @@
           <t>2025-10-28</t>
         </is>
       </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>barksprätt på gammal gran</t>
+        </is>
+      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4277,10 +4278,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129742261</v>
+        <v>129744558</v>
       </c>
       <c r="B36" t="n">
-        <v>57736</v>
+        <v>91588</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4288,27 +4289,30 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4316,10 +4320,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>789192</v>
+        <v>789368</v>
       </c>
       <c r="R36" t="n">
-        <v>7151225</v>
+        <v>7151214</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4354,17 +4358,13 @@
           <t>2025-10-28</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>barksprätt på gammal gran</t>
-        </is>
-      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4383,10 +4383,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129744558</v>
+        <v>129742429</v>
       </c>
       <c r="B37" t="n">
-        <v>91588</v>
+        <v>79076</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4394,27 +4394,27 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
@@ -4425,10 +4425,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>789368</v>
+        <v>789351</v>
       </c>
       <c r="R37" t="n">
-        <v>7151214</v>
+        <v>7151276</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4703,10 +4703,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129745167</v>
+        <v>129745946</v>
       </c>
       <c r="B40" t="n">
-        <v>79076</v>
+        <v>82911</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4714,27 +4714,27 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
@@ -4745,10 +4745,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>789233</v>
+        <v>789208</v>
       </c>
       <c r="R40" t="n">
-        <v>7151272</v>
+        <v>7151157</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4808,10 +4808,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129745946</v>
+        <v>129745167</v>
       </c>
       <c r="B41" t="n">
-        <v>82911</v>
+        <v>79076</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4819,27 +4819,27 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
@@ -4850,10 +4850,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>789208</v>
+        <v>789233</v>
       </c>
       <c r="R41" t="n">
-        <v>7151157</v>
+        <v>7151272</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>

--- a/artfynd/A 50406-2025 artfynd.xlsx
+++ b/artfynd/A 50406-2025 artfynd.xlsx
@@ -1163,7 +1163,7 @@
         <v>129742487</v>
       </c>
       <c r="B7" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1265,10 +1265,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129745889</v>
+        <v>129745363</v>
       </c>
       <c r="B8" t="n">
-        <v>82911</v>
+        <v>57733</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1276,30 +1276,31 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1312</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1307,10 +1308,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>789222</v>
+        <v>789241</v>
       </c>
       <c r="R8" t="n">
-        <v>7151172</v>
+        <v>7151185</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1345,13 +1346,17 @@
           <t>2025-10-28</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>på nära håll</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1370,10 +1375,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129745363</v>
+        <v>129745889</v>
       </c>
       <c r="B9" t="n">
-        <v>57733</v>
+        <v>82916</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1381,31 +1386,30 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>1312</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1413,10 +1417,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>789241</v>
+        <v>789222</v>
       </c>
       <c r="R9" t="n">
-        <v>7151185</v>
+        <v>7151172</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1451,17 +1455,13 @@
           <t>2025-10-28</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>på nära håll</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1480,10 +1480,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129743137</v>
+        <v>129742539</v>
       </c>
       <c r="B10" t="n">
-        <v>57736</v>
+        <v>91593</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1491,31 +1491,30 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1523,10 +1522,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>789220</v>
+        <v>789298</v>
       </c>
       <c r="R10" t="n">
-        <v>7151136</v>
+        <v>7151197</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1563,7 +1562,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>färska ringhack som utgörs av små punkthack på en gran</t>
+          <t>på samma låga som rynkskinn</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1572,6 +1571,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1590,10 +1590,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129742539</v>
+        <v>129743137</v>
       </c>
       <c r="B11" t="n">
-        <v>91588</v>
+        <v>57736</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1601,30 +1601,31 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1632,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>789298</v>
+        <v>789220</v>
       </c>
       <c r="R11" t="n">
-        <v>7151197</v>
+        <v>7151136</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1672,7 +1673,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>på samma låga som rynkskinn</t>
+          <t>färska ringhack som utgörs av små punkthack på en gran</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1681,7 +1682,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1700,10 +1700,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129745950</v>
+        <v>129743913</v>
       </c>
       <c r="B12" t="n">
-        <v>82911</v>
+        <v>57736</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1711,30 +1711,31 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1742,10 +1743,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>789199</v>
+        <v>789283</v>
       </c>
       <c r="R12" t="n">
-        <v>7151153</v>
+        <v>7151180</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1780,13 +1781,17 @@
           <t>2025-10-28</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>ringhack på gammal gran</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1805,10 +1810,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129745347</v>
+        <v>129742521</v>
       </c>
       <c r="B13" t="n">
-        <v>79076</v>
+        <v>57736</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1816,30 +1821,31 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1847,10 +1853,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>789248</v>
+        <v>789331</v>
       </c>
       <c r="R13" t="n">
-        <v>7151191</v>
+        <v>7151248</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1887,7 +1893,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>på stammen av en tall</t>
+          <t>ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1896,7 +1902,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1915,10 +1920,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129745328</v>
+        <v>129745950</v>
       </c>
       <c r="B14" t="n">
-        <v>79076</v>
+        <v>82916</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1926,27 +1931,27 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -1957,10 +1962,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>789227</v>
+        <v>789199</v>
       </c>
       <c r="R14" t="n">
-        <v>7151210</v>
+        <v>7151153</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2020,10 +2025,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129743913</v>
+        <v>129745347</v>
       </c>
       <c r="B15" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2031,31 +2036,30 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2063,10 +2067,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>789283</v>
+        <v>789248</v>
       </c>
       <c r="R15" t="n">
-        <v>7151180</v>
+        <v>7151191</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2103,7 +2107,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>ringhack på gammal gran</t>
+          <t>på stammen av en tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2112,6 +2116,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2130,10 +2135,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129742521</v>
+        <v>129745328</v>
       </c>
       <c r="B16" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2141,31 +2146,30 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2173,10 +2177,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>789331</v>
+        <v>789227</v>
       </c>
       <c r="R16" t="n">
-        <v>7151248</v>
+        <v>7151210</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2211,17 +2215,13 @@
           <t>2025-10-28</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>ringhack på tall</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2240,10 +2240,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129742406</v>
+        <v>129745466</v>
       </c>
       <c r="B17" t="n">
-        <v>79076</v>
+        <v>57733</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2251,30 +2251,31 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2282,10 +2283,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>789267</v>
+        <v>789212</v>
       </c>
       <c r="R17" t="n">
-        <v>7151238</v>
+        <v>7151164</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2320,13 +2321,17 @@
           <t>2025-10-28</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>bohål i gran</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2348,7 +2353,7 @@
         <v>129746089</v>
       </c>
       <c r="B18" t="n">
-        <v>82911</v>
+        <v>82916</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2450,10 +2455,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129745466</v>
+        <v>129742406</v>
       </c>
       <c r="B19" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2461,31 +2466,30 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2493,10 +2497,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>789212</v>
+        <v>789267</v>
       </c>
       <c r="R19" t="n">
-        <v>7151164</v>
+        <v>7151238</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2531,17 +2535,13 @@
           <t>2025-10-28</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>bohål i gran</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2675,7 +2675,7 @@
         <v>129745993</v>
       </c>
       <c r="B21" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2785,7 +2785,7 @@
         <v>129742631</v>
       </c>
       <c r="B22" t="n">
-        <v>91539</v>
+        <v>91544</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2890,7 +2890,7 @@
         <v>129745192</v>
       </c>
       <c r="B23" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2992,37 +2992,42 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129742557</v>
+        <v>129745532</v>
       </c>
       <c r="B24" t="n">
-        <v>92041</v>
+        <v>57733</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1209</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3030,10 +3035,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>789298</v>
+        <v>789215</v>
       </c>
       <c r="R24" t="n">
-        <v>7151197</v>
+        <v>7151159</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3070,7 +3075,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>på samma granlåga som ullticka</t>
+          <t>hack i låga</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3079,7 +3084,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3098,42 +3102,37 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129745532</v>
+        <v>129742557</v>
       </c>
       <c r="B25" t="n">
-        <v>57733</v>
+        <v>92046</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>1209</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3141,10 +3140,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>789215</v>
+        <v>789298</v>
       </c>
       <c r="R25" t="n">
-        <v>7151159</v>
+        <v>7151197</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3181,7 +3180,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>hack i låga</t>
+          <t>på samma granlåga som ullticka</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3190,6 +3189,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3208,38 +3208,38 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129745563</v>
+        <v>129745551</v>
       </c>
       <c r="B26" t="n">
-        <v>91552</v>
+        <v>79081</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
@@ -3250,10 +3250,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>789198</v>
+        <v>789219</v>
       </c>
       <c r="R26" t="n">
-        <v>7151158</v>
+        <v>7151168</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3313,42 +3313,41 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129744135</v>
+        <v>129745563</v>
       </c>
       <c r="B27" t="n">
-        <v>57736</v>
+        <v>91557</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3356,10 +3355,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>789284</v>
+        <v>789198</v>
       </c>
       <c r="R27" t="n">
-        <v>7151167</v>
+        <v>7151158</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3394,17 +3393,13 @@
           <t>2025-10-28</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>äldre ringhack på gran</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3423,10 +3418,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129745551</v>
+        <v>129744135</v>
       </c>
       <c r="B28" t="n">
-        <v>79076</v>
+        <v>57736</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3434,30 +3429,31 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3465,10 +3461,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>789219</v>
+        <v>789284</v>
       </c>
       <c r="R28" t="n">
-        <v>7151168</v>
+        <v>7151167</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3503,13 +3499,17 @@
           <t>2025-10-28</t>
         </is>
       </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>äldre ringhack på gran</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3528,41 +3528,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129742620</v>
+        <v>129745383</v>
       </c>
       <c r="B29" t="n">
-        <v>91552</v>
+        <v>79081</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr"/>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3570,10 +3574,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>789294</v>
+        <v>789239</v>
       </c>
       <c r="R29" t="n">
-        <v>7151188</v>
+        <v>7151169</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3606,6 +3610,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>fertil</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3633,10 +3642,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129745383</v>
+        <v>129745427</v>
       </c>
       <c r="B30" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3667,11 +3676,7 @@
           <t>bålar</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3679,7 +3684,7 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>789239</v>
+        <v>789221</v>
       </c>
       <c r="R30" t="n">
         <v>7151169</v>
@@ -3715,11 +3720,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-10-28</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>fertil</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3747,38 +3747,38 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129745427</v>
+        <v>129742620</v>
       </c>
       <c r="B31" t="n">
-        <v>79076</v>
+        <v>91557</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
@@ -3789,10 +3789,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>789221</v>
+        <v>789294</v>
       </c>
       <c r="R31" t="n">
-        <v>7151169</v>
+        <v>7151188</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3852,10 +3852,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129742300</v>
+        <v>129745155</v>
       </c>
       <c r="B32" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3863,31 +3863,30 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -3895,10 +3894,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>789197</v>
+        <v>789288</v>
       </c>
       <c r="R32" t="n">
-        <v>7151175</v>
+        <v>7151234</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3933,17 +3932,13 @@
           <t>2025-10-28</t>
         </is>
       </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>hål i tall</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -3962,10 +3957,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129745155</v>
+        <v>129742300</v>
       </c>
       <c r="B33" t="n">
-        <v>79076</v>
+        <v>57733</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3973,30 +3968,31 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4004,10 +4000,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>789288</v>
+        <v>789197</v>
       </c>
       <c r="R33" t="n">
-        <v>7151234</v>
+        <v>7151175</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4042,13 +4038,17 @@
           <t>2025-10-28</t>
         </is>
       </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>hål i tall</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4070,7 +4070,7 @@
         <v>129742254</v>
       </c>
       <c r="B34" t="n">
-        <v>79108</v>
+        <v>79113</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4172,10 +4172,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129742261</v>
+        <v>129744558</v>
       </c>
       <c r="B35" t="n">
-        <v>57736</v>
+        <v>91593</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4183,27 +4183,30 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4211,10 +4214,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>789192</v>
+        <v>789368</v>
       </c>
       <c r="R35" t="n">
-        <v>7151225</v>
+        <v>7151214</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4249,17 +4252,13 @@
           <t>2025-10-28</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>barksprätt på gammal gran</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4278,10 +4277,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129744558</v>
+        <v>129742429</v>
       </c>
       <c r="B36" t="n">
-        <v>91588</v>
+        <v>79081</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4289,27 +4288,27 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
@@ -4320,10 +4319,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>789368</v>
+        <v>789351</v>
       </c>
       <c r="R36" t="n">
-        <v>7151214</v>
+        <v>7151276</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4383,10 +4382,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129742429</v>
+        <v>129742261</v>
       </c>
       <c r="B37" t="n">
-        <v>79076</v>
+        <v>57736</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4394,30 +4393,27 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4425,10 +4421,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>789351</v>
+        <v>789192</v>
       </c>
       <c r="R37" t="n">
-        <v>7151276</v>
+        <v>7151225</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4463,13 +4459,17 @@
           <t>2025-10-28</t>
         </is>
       </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>barksprätt på gammal gran</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4491,7 +4491,7 @@
         <v>129742447</v>
       </c>
       <c r="B38" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4601,7 +4601,7 @@
         <v>129745159</v>
       </c>
       <c r="B39" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4706,7 +4706,7 @@
         <v>129745946</v>
       </c>
       <c r="B40" t="n">
-        <v>82911</v>
+        <v>82916</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4811,7 +4811,7 @@
         <v>129745167</v>
       </c>
       <c r="B41" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4913,38 +4913,38 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129742518</v>
+        <v>129742516</v>
       </c>
       <c r="B42" t="n">
-        <v>91552</v>
+        <v>79081</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K42" t="inlineStr"/>
@@ -4955,10 +4955,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>789345</v>
+        <v>789348</v>
       </c>
       <c r="R42" t="n">
-        <v>7151261</v>
+        <v>7151255</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5018,38 +5018,38 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129742516</v>
+        <v>129742518</v>
       </c>
       <c r="B43" t="n">
-        <v>79076</v>
+        <v>91557</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K43" t="inlineStr"/>
@@ -5060,10 +5060,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>789348</v>
+        <v>789345</v>
       </c>
       <c r="R43" t="n">
-        <v>7151255</v>
+        <v>7151261</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>

--- a/artfynd/A 50406-2025 artfynd.xlsx
+++ b/artfynd/A 50406-2025 artfynd.xlsx
@@ -1265,10 +1265,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129745363</v>
+        <v>129745889</v>
       </c>
       <c r="B8" t="n">
-        <v>57733</v>
+        <v>82916</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1276,31 +1276,30 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>1312</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1308,10 +1307,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>789241</v>
+        <v>789222</v>
       </c>
       <c r="R8" t="n">
-        <v>7151185</v>
+        <v>7151172</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1346,17 +1345,13 @@
           <t>2025-10-28</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>på nära håll</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1375,10 +1370,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129745889</v>
+        <v>129745363</v>
       </c>
       <c r="B9" t="n">
-        <v>82916</v>
+        <v>57733</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1386,30 +1381,31 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1312</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1417,10 +1413,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>789222</v>
+        <v>789241</v>
       </c>
       <c r="R9" t="n">
-        <v>7151172</v>
+        <v>7151185</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1455,13 +1451,17 @@
           <t>2025-10-28</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>på nära håll</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1480,10 +1480,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129742539</v>
+        <v>129743137</v>
       </c>
       <c r="B10" t="n">
-        <v>91593</v>
+        <v>57736</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1491,30 +1491,31 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1522,10 +1523,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>789298</v>
+        <v>789220</v>
       </c>
       <c r="R10" t="n">
-        <v>7151197</v>
+        <v>7151136</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1562,7 +1563,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>på samma låga som rynkskinn</t>
+          <t>färska ringhack som utgörs av små punkthack på en gran</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1571,7 +1572,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1590,10 +1590,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129743137</v>
+        <v>129742539</v>
       </c>
       <c r="B11" t="n">
-        <v>57736</v>
+        <v>91593</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1601,31 +1601,30 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1633,10 +1632,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>789220</v>
+        <v>789298</v>
       </c>
       <c r="R11" t="n">
-        <v>7151136</v>
+        <v>7151197</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1673,7 +1672,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>färska ringhack som utgörs av små punkthack på en gran</t>
+          <t>på samma låga som rynkskinn</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1682,6 +1681,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1700,10 +1700,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129743913</v>
+        <v>129745950</v>
       </c>
       <c r="B12" t="n">
-        <v>57736</v>
+        <v>82916</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1711,31 +1711,30 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1743,10 +1742,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>789283</v>
+        <v>789199</v>
       </c>
       <c r="R12" t="n">
-        <v>7151180</v>
+        <v>7151153</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1781,17 +1780,13 @@
           <t>2025-10-28</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>ringhack på gammal gran</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1810,7 +1805,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129742521</v>
+        <v>129743913</v>
       </c>
       <c r="B13" t="n">
         <v>57736</v>
@@ -1843,7 +1838,7 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -1853,10 +1848,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>789331</v>
+        <v>789283</v>
       </c>
       <c r="R13" t="n">
-        <v>7151248</v>
+        <v>7151180</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1893,7 +1888,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>ringhack på tall</t>
+          <t>ringhack på gammal gran</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1920,10 +1915,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129745950</v>
+        <v>129745347</v>
       </c>
       <c r="B14" t="n">
-        <v>82916</v>
+        <v>79081</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1931,27 +1926,27 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -1962,10 +1957,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>789199</v>
+        <v>789248</v>
       </c>
       <c r="R14" t="n">
-        <v>7151153</v>
+        <v>7151191</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1998,6 +1993,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>på stammen av en tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2025,7 +2025,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129745347</v>
+        <v>129745328</v>
       </c>
       <c r="B15" t="n">
         <v>79081</v>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>789248</v>
+        <v>789227</v>
       </c>
       <c r="R15" t="n">
-        <v>7151191</v>
+        <v>7151210</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2103,11 +2103,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-10-28</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>på stammen av en tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2135,10 +2130,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129745328</v>
+        <v>129742521</v>
       </c>
       <c r="B16" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2146,30 +2141,31 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2177,10 +2173,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>789227</v>
+        <v>789331</v>
       </c>
       <c r="R16" t="n">
-        <v>7151210</v>
+        <v>7151248</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2215,13 +2211,17 @@
           <t>2025-10-28</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>ringhack på tall</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2240,10 +2240,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129745466</v>
+        <v>129746089</v>
       </c>
       <c r="B17" t="n">
-        <v>57733</v>
+        <v>82916</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2251,31 +2251,30 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>1312</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2283,10 +2282,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>789212</v>
+        <v>789203</v>
       </c>
       <c r="R17" t="n">
-        <v>7151164</v>
+        <v>7151242</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2321,17 +2320,13 @@
           <t>2025-10-28</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>bohål i gran</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2350,10 +2345,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129746089</v>
+        <v>129742406</v>
       </c>
       <c r="B18" t="n">
-        <v>82916</v>
+        <v>79081</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2361,27 +2356,27 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -2392,10 +2387,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>789203</v>
+        <v>789267</v>
       </c>
       <c r="R18" t="n">
-        <v>7151242</v>
+        <v>7151238</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2455,10 +2450,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129742406</v>
+        <v>129745466</v>
       </c>
       <c r="B19" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2466,30 +2461,31 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2497,10 +2493,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>789267</v>
+        <v>789212</v>
       </c>
       <c r="R19" t="n">
-        <v>7151238</v>
+        <v>7151164</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2535,13 +2531,17 @@
           <t>2025-10-28</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>bohål i gran</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2672,10 +2672,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129745993</v>
+        <v>129742631</v>
       </c>
       <c r="B21" t="n">
-        <v>79081</v>
+        <v>91544</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2683,27 +2683,27 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>112</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -2714,10 +2714,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>789196</v>
+        <v>789289</v>
       </c>
       <c r="R21" t="n">
-        <v>7151151</v>
+        <v>7151198</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2750,11 +2750,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-10-28</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>ca 70cm lång bål!</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2782,10 +2777,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129742631</v>
+        <v>129745993</v>
       </c>
       <c r="B22" t="n">
-        <v>91544</v>
+        <v>79081</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2793,27 +2788,27 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>112</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -2824,10 +2819,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>789289</v>
+        <v>789196</v>
       </c>
       <c r="R22" t="n">
-        <v>7151198</v>
+        <v>7151151</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2860,6 +2855,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>ca 70cm lång bål!</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2992,42 +2992,37 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129745532</v>
+        <v>129742557</v>
       </c>
       <c r="B24" t="n">
-        <v>57733</v>
+        <v>92046</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>1209</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3035,10 +3030,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>789215</v>
+        <v>789298</v>
       </c>
       <c r="R24" t="n">
-        <v>7151159</v>
+        <v>7151197</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3075,7 +3070,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>hack i låga</t>
+          <t>på samma granlåga som ullticka</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3084,6 +3079,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3102,37 +3098,42 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129742557</v>
+        <v>129745532</v>
       </c>
       <c r="B25" t="n">
-        <v>92046</v>
+        <v>57733</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1209</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3140,10 +3141,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>789298</v>
+        <v>789215</v>
       </c>
       <c r="R25" t="n">
-        <v>7151197</v>
+        <v>7151159</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3180,7 +3181,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>på samma granlåga som ullticka</t>
+          <t>hack i låga</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3189,7 +3190,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3313,41 +3313,42 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129745563</v>
+        <v>129744135</v>
       </c>
       <c r="B27" t="n">
-        <v>91557</v>
+        <v>57736</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3355,10 +3356,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>789198</v>
+        <v>789284</v>
       </c>
       <c r="R27" t="n">
-        <v>7151158</v>
+        <v>7151167</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3393,13 +3394,17 @@
           <t>2025-10-28</t>
         </is>
       </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>äldre ringhack på gran</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3418,42 +3423,41 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129744135</v>
+        <v>129745563</v>
       </c>
       <c r="B28" t="n">
-        <v>57736</v>
+        <v>91557</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3461,10 +3465,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>789284</v>
+        <v>789198</v>
       </c>
       <c r="R28" t="n">
-        <v>7151167</v>
+        <v>7151158</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3499,17 +3503,13 @@
           <t>2025-10-28</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>äldre ringhack på gran</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3528,45 +3528,41 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129745383</v>
+        <v>129742620</v>
       </c>
       <c r="B29" t="n">
-        <v>79081</v>
+        <v>91557</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3574,10 +3570,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>789239</v>
+        <v>789294</v>
       </c>
       <c r="R29" t="n">
-        <v>7151169</v>
+        <v>7151188</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3610,11 +3606,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-10-28</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>fertil</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3642,7 +3633,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129745427</v>
+        <v>129745383</v>
       </c>
       <c r="B30" t="n">
         <v>79081</v>
@@ -3676,7 +3667,11 @@
           <t>bålar</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3684,7 +3679,7 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>789221</v>
+        <v>789239</v>
       </c>
       <c r="R30" t="n">
         <v>7151169</v>
@@ -3720,6 +3715,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>fertil</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3747,38 +3747,38 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129742620</v>
+        <v>129745427</v>
       </c>
       <c r="B31" t="n">
-        <v>91557</v>
+        <v>79081</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
@@ -3789,10 +3789,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>789294</v>
+        <v>789221</v>
       </c>
       <c r="R31" t="n">
-        <v>7151188</v>
+        <v>7151169</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3852,10 +3852,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129745155</v>
+        <v>129742300</v>
       </c>
       <c r="B32" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3863,30 +3863,31 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -3894,10 +3895,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>789288</v>
+        <v>789197</v>
       </c>
       <c r="R32" t="n">
-        <v>7151234</v>
+        <v>7151175</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3932,13 +3933,17 @@
           <t>2025-10-28</t>
         </is>
       </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>hål i tall</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -3957,10 +3962,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129742300</v>
+        <v>129745155</v>
       </c>
       <c r="B33" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3968,31 +3973,30 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4000,10 +4004,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>789197</v>
+        <v>789288</v>
       </c>
       <c r="R33" t="n">
-        <v>7151175</v>
+        <v>7151234</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4038,17 +4042,13 @@
           <t>2025-10-28</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>hål i tall</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4703,10 +4703,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129745946</v>
+        <v>129745167</v>
       </c>
       <c r="B40" t="n">
-        <v>82916</v>
+        <v>79081</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4714,27 +4714,27 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
@@ -4745,10 +4745,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>789208</v>
+        <v>789233</v>
       </c>
       <c r="R40" t="n">
-        <v>7151157</v>
+        <v>7151272</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4808,10 +4808,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129745167</v>
+        <v>129745946</v>
       </c>
       <c r="B41" t="n">
-        <v>79081</v>
+        <v>82916</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4819,27 +4819,27 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
@@ -4850,10 +4850,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>789233</v>
+        <v>789208</v>
       </c>
       <c r="R41" t="n">
-        <v>7151272</v>
+        <v>7151157</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>

--- a/artfynd/A 50406-2025 artfynd.xlsx
+++ b/artfynd/A 50406-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY43"/>
+  <dimension ref="A1:AY44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1480,10 +1480,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129743137</v>
+        <v>129742539</v>
       </c>
       <c r="B10" t="n">
-        <v>57736</v>
+        <v>91593</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1491,31 +1491,30 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1523,10 +1522,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>789220</v>
+        <v>789298</v>
       </c>
       <c r="R10" t="n">
-        <v>7151136</v>
+        <v>7151197</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1563,7 +1562,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>färska ringhack som utgörs av små punkthack på en gran</t>
+          <t>på samma låga som rynkskinn</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1572,6 +1571,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1590,10 +1590,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129742539</v>
+        <v>129743137</v>
       </c>
       <c r="B11" t="n">
-        <v>91593</v>
+        <v>57736</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1601,30 +1601,31 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1632,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>789298</v>
+        <v>789220</v>
       </c>
       <c r="R11" t="n">
-        <v>7151197</v>
+        <v>7151136</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1672,7 +1673,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>på samma låga som rynkskinn</t>
+          <t>färska ringhack som utgörs av små punkthack på en gran</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1681,7 +1682,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1805,10 +1805,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129743913</v>
+        <v>129745347</v>
       </c>
       <c r="B13" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1816,31 +1816,30 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1848,10 +1847,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>789283</v>
+        <v>789248</v>
       </c>
       <c r="R13" t="n">
-        <v>7151180</v>
+        <v>7151191</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1888,7 +1887,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>ringhack på gammal gran</t>
+          <t>på stammen av en tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1897,6 +1896,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1915,7 +1915,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129745347</v>
+        <v>129745328</v>
       </c>
       <c r="B14" t="n">
         <v>79081</v>
@@ -1957,10 +1957,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>789248</v>
+        <v>789227</v>
       </c>
       <c r="R14" t="n">
-        <v>7151191</v>
+        <v>7151210</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1993,11 +1993,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-28</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>på stammen av en tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2025,10 +2020,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129745328</v>
+        <v>129743913</v>
       </c>
       <c r="B15" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2036,30 +2031,31 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2067,10 +2063,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>789227</v>
+        <v>789283</v>
       </c>
       <c r="R15" t="n">
-        <v>7151210</v>
+        <v>7151180</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2105,13 +2101,17 @@
           <t>2025-10-28</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>ringhack på gammal gran</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2240,10 +2240,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129746089</v>
+        <v>129745466</v>
       </c>
       <c r="B17" t="n">
-        <v>82916</v>
+        <v>57733</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2251,30 +2251,31 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1312</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2282,10 +2283,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>789203</v>
+        <v>789212</v>
       </c>
       <c r="R17" t="n">
-        <v>7151242</v>
+        <v>7151164</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2320,13 +2321,17 @@
           <t>2025-10-28</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>bohål i gran</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2450,10 +2455,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129745466</v>
+        <v>129746089</v>
       </c>
       <c r="B19" t="n">
-        <v>57733</v>
+        <v>82916</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2461,31 +2466,30 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>1312</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2493,10 +2497,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>789212</v>
+        <v>789203</v>
       </c>
       <c r="R19" t="n">
-        <v>7151164</v>
+        <v>7151242</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2531,17 +2535,13 @@
           <t>2025-10-28</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>bohål i gran</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2672,10 +2672,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129742631</v>
+        <v>129745993</v>
       </c>
       <c r="B21" t="n">
-        <v>91544</v>
+        <v>79081</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2683,27 +2683,27 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>112</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -2714,10 +2714,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>789289</v>
+        <v>789196</v>
       </c>
       <c r="R21" t="n">
-        <v>7151198</v>
+        <v>7151151</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2750,6 +2750,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>ca 70cm lång bål!</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2777,10 +2782,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129745993</v>
+        <v>129742631</v>
       </c>
       <c r="B22" t="n">
-        <v>79081</v>
+        <v>91544</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2788,27 +2793,27 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>112</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -2819,10 +2824,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>789196</v>
+        <v>789289</v>
       </c>
       <c r="R22" t="n">
-        <v>7151151</v>
+        <v>7151198</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2855,11 +2860,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-28</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>ca 70cm lång bål!</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3208,38 +3208,38 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129745551</v>
+        <v>129745563</v>
       </c>
       <c r="B26" t="n">
-        <v>79081</v>
+        <v>91557</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
@@ -3250,10 +3250,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>789219</v>
+        <v>789198</v>
       </c>
       <c r="R26" t="n">
-        <v>7151168</v>
+        <v>7151158</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3423,38 +3423,38 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129745563</v>
+        <v>129745551</v>
       </c>
       <c r="B28" t="n">
-        <v>91557</v>
+        <v>79081</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
@@ -3465,10 +3465,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>789198</v>
+        <v>789219</v>
       </c>
       <c r="R28" t="n">
-        <v>7151158</v>
+        <v>7151168</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3528,38 +3528,38 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129742620</v>
+        <v>129745427</v>
       </c>
       <c r="B29" t="n">
-        <v>91557</v>
+        <v>79081</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
@@ -3570,10 +3570,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>789294</v>
+        <v>789221</v>
       </c>
       <c r="R29" t="n">
-        <v>7151188</v>
+        <v>7151169</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3633,45 +3633,41 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129745383</v>
+        <v>129742620</v>
       </c>
       <c r="B30" t="n">
-        <v>79081</v>
+        <v>91557</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr">
         <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3679,10 +3675,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>789239</v>
+        <v>789294</v>
       </c>
       <c r="R30" t="n">
-        <v>7151169</v>
+        <v>7151188</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3715,11 +3711,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-10-28</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>fertil</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3747,7 +3738,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129745427</v>
+        <v>129745383</v>
       </c>
       <c r="B31" t="n">
         <v>79081</v>
@@ -3781,7 +3772,11 @@
           <t>bålar</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3789,7 +3784,7 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>789221</v>
+        <v>789239</v>
       </c>
       <c r="R31" t="n">
         <v>7151169</v>
@@ -3825,6 +3820,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>fertil</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3852,10 +3852,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129742300</v>
+        <v>129745155</v>
       </c>
       <c r="B32" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3863,31 +3863,30 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -3895,10 +3894,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>789197</v>
+        <v>789288</v>
       </c>
       <c r="R32" t="n">
-        <v>7151175</v>
+        <v>7151234</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3933,17 +3932,13 @@
           <t>2025-10-28</t>
         </is>
       </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>hål i tall</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -3962,10 +3957,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129745155</v>
+        <v>129742300</v>
       </c>
       <c r="B33" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3973,30 +3968,31 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4004,10 +4000,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>789288</v>
+        <v>789197</v>
       </c>
       <c r="R33" t="n">
-        <v>7151234</v>
+        <v>7151175</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4042,13 +4038,17 @@
           <t>2025-10-28</t>
         </is>
       </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>hål i tall</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4488,7 +4488,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129742447</v>
+        <v>129745159</v>
       </c>
       <c r="B38" t="n">
         <v>79081</v>
@@ -4530,10 +4530,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>789380</v>
+        <v>789266</v>
       </c>
       <c r="R38" t="n">
-        <v>7151245</v>
+        <v>7151263</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4566,11 +4566,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-10-28</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>på stammen av en tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4598,7 +4593,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129745159</v>
+        <v>129742447</v>
       </c>
       <c r="B39" t="n">
         <v>79081</v>
@@ -4640,10 +4635,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>789266</v>
+        <v>789380</v>
       </c>
       <c r="R39" t="n">
-        <v>7151263</v>
+        <v>7151245</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4676,6 +4671,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>på stammen av en tall</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4703,10 +4703,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129745167</v>
+        <v>129745946</v>
       </c>
       <c r="B40" t="n">
-        <v>79081</v>
+        <v>82916</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4714,27 +4714,27 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
@@ -4745,10 +4745,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>789233</v>
+        <v>789208</v>
       </c>
       <c r="R40" t="n">
-        <v>7151272</v>
+        <v>7151157</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4808,10 +4808,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129745946</v>
+        <v>129745167</v>
       </c>
       <c r="B41" t="n">
-        <v>82916</v>
+        <v>79081</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4819,27 +4819,27 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
@@ -4850,10 +4850,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>789208</v>
+        <v>789233</v>
       </c>
       <c r="R41" t="n">
-        <v>7151157</v>
+        <v>7151272</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5121,6 +5121,116 @@
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>129825892</v>
+      </c>
+      <c r="B44" t="n">
+        <v>57736</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Öster om Boströmberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>789198</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7151138</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Robertsfors</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Nysätra</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>barken avfläkt på gran med insektsangrepp. Kan det vara tretåig hackspett som gjort det?</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 50406-2025 artfynd.xlsx
+++ b/artfynd/A 50406-2025 artfynd.xlsx
@@ -2240,10 +2240,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129745466</v>
+        <v>129746089</v>
       </c>
       <c r="B17" t="n">
-        <v>57733</v>
+        <v>82916</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2251,31 +2251,30 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>1312</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2283,10 +2282,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>789212</v>
+        <v>789203</v>
       </c>
       <c r="R17" t="n">
-        <v>7151164</v>
+        <v>7151242</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2321,17 +2320,13 @@
           <t>2025-10-28</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>bohål i gran</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2455,10 +2450,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129746089</v>
+        <v>129745466</v>
       </c>
       <c r="B19" t="n">
-        <v>82916</v>
+        <v>57733</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2466,30 +2461,31 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1312</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2497,10 +2493,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>789203</v>
+        <v>789212</v>
       </c>
       <c r="R19" t="n">
-        <v>7151242</v>
+        <v>7151164</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2535,13 +2531,17 @@
           <t>2025-10-28</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>bohål i gran</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2672,10 +2672,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129745993</v>
+        <v>129742631</v>
       </c>
       <c r="B21" t="n">
-        <v>79081</v>
+        <v>91544</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2683,27 +2683,27 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>112</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -2714,10 +2714,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>789196</v>
+        <v>789289</v>
       </c>
       <c r="R21" t="n">
-        <v>7151151</v>
+        <v>7151198</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2750,11 +2750,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-10-28</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>ca 70cm lång bål!</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2782,10 +2777,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129742631</v>
+        <v>129745993</v>
       </c>
       <c r="B22" t="n">
-        <v>91544</v>
+        <v>79081</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2793,27 +2788,27 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>112</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -2824,10 +2819,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>789289</v>
+        <v>789196</v>
       </c>
       <c r="R22" t="n">
-        <v>7151198</v>
+        <v>7151151</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2860,6 +2855,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>ca 70cm lång bål!</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3208,38 +3208,38 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129745563</v>
+        <v>129745551</v>
       </c>
       <c r="B26" t="n">
-        <v>91557</v>
+        <v>79081</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
@@ -3250,10 +3250,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>789198</v>
+        <v>789219</v>
       </c>
       <c r="R26" t="n">
-        <v>7151158</v>
+        <v>7151168</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3313,42 +3313,41 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129744135</v>
+        <v>129745563</v>
       </c>
       <c r="B27" t="n">
-        <v>57736</v>
+        <v>91557</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3356,10 +3355,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>789284</v>
+        <v>789198</v>
       </c>
       <c r="R27" t="n">
-        <v>7151167</v>
+        <v>7151158</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3394,17 +3393,13 @@
           <t>2025-10-28</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>äldre ringhack på gran</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3423,10 +3418,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129745551</v>
+        <v>129744135</v>
       </c>
       <c r="B28" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3434,30 +3429,31 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3465,10 +3461,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>789219</v>
+        <v>789284</v>
       </c>
       <c r="R28" t="n">
-        <v>7151168</v>
+        <v>7151167</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3503,13 +3499,17 @@
           <t>2025-10-28</t>
         </is>
       </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>äldre ringhack på gran</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3528,38 +3528,38 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129745427</v>
+        <v>129742620</v>
       </c>
       <c r="B29" t="n">
-        <v>79081</v>
+        <v>91557</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
@@ -3570,10 +3570,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>789221</v>
+        <v>789294</v>
       </c>
       <c r="R29" t="n">
-        <v>7151169</v>
+        <v>7151188</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3633,38 +3633,38 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129742620</v>
+        <v>129745427</v>
       </c>
       <c r="B30" t="n">
-        <v>91557</v>
+        <v>79081</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
@@ -3675,10 +3675,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>789294</v>
+        <v>789221</v>
       </c>
       <c r="R30" t="n">
-        <v>7151188</v>
+        <v>7151169</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4172,10 +4172,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129744558</v>
+        <v>129742429</v>
       </c>
       <c r="B35" t="n">
-        <v>91593</v>
+        <v>79081</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4183,27 +4183,27 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
@@ -4214,10 +4214,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>789368</v>
+        <v>789351</v>
       </c>
       <c r="R35" t="n">
-        <v>7151214</v>
+        <v>7151276</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4277,10 +4277,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129742429</v>
+        <v>129744558</v>
       </c>
       <c r="B36" t="n">
-        <v>79081</v>
+        <v>91593</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4288,27 +4288,27 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
@@ -4319,10 +4319,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>789351</v>
+        <v>789368</v>
       </c>
       <c r="R36" t="n">
-        <v>7151276</v>
+        <v>7151214</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4488,7 +4488,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129745159</v>
+        <v>129742447</v>
       </c>
       <c r="B38" t="n">
         <v>79081</v>
@@ -4530,10 +4530,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>789266</v>
+        <v>789380</v>
       </c>
       <c r="R38" t="n">
-        <v>7151263</v>
+        <v>7151245</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4566,6 +4566,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>på stammen av en tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4593,7 +4598,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129742447</v>
+        <v>129745159</v>
       </c>
       <c r="B39" t="n">
         <v>79081</v>
@@ -4635,10 +4640,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>789380</v>
+        <v>789266</v>
       </c>
       <c r="R39" t="n">
-        <v>7151245</v>
+        <v>7151263</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4671,11 +4676,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-10-28</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>på stammen av en tall</t>
         </is>
       </c>
       <c r="AD39" t="b">

--- a/artfynd/A 50406-2025 artfynd.xlsx
+++ b/artfynd/A 50406-2025 artfynd.xlsx
@@ -1483,7 +1483,7 @@
         <v>129742539</v>
       </c>
       <c r="B10" t="n">
-        <v>91593</v>
+        <v>91597</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1700,10 +1700,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129745950</v>
+        <v>129742521</v>
       </c>
       <c r="B12" t="n">
-        <v>82916</v>
+        <v>57736</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1711,30 +1711,31 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1742,10 +1743,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>789199</v>
+        <v>789331</v>
       </c>
       <c r="R12" t="n">
-        <v>7151153</v>
+        <v>7151248</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1780,13 +1781,17 @@
           <t>2025-10-28</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>ringhack på tall</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1805,10 +1810,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129745347</v>
+        <v>129743913</v>
       </c>
       <c r="B13" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1816,30 +1821,31 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1847,10 +1853,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>789248</v>
+        <v>789283</v>
       </c>
       <c r="R13" t="n">
-        <v>7151191</v>
+        <v>7151180</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1887,7 +1893,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>på stammen av en tall</t>
+          <t>ringhack på gammal gran</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1896,7 +1902,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1915,10 +1920,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129745328</v>
+        <v>129745950</v>
       </c>
       <c r="B14" t="n">
-        <v>79081</v>
+        <v>82916</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1926,27 +1931,27 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -1957,10 +1962,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>789227</v>
+        <v>789199</v>
       </c>
       <c r="R14" t="n">
-        <v>7151210</v>
+        <v>7151153</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2020,10 +2025,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129743913</v>
+        <v>129745347</v>
       </c>
       <c r="B15" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2031,31 +2036,30 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2063,10 +2067,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>789283</v>
+        <v>789248</v>
       </c>
       <c r="R15" t="n">
-        <v>7151180</v>
+        <v>7151191</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2103,7 +2107,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>ringhack på gammal gran</t>
+          <t>på stammen av en tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2112,6 +2116,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2130,10 +2135,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129742521</v>
+        <v>129745328</v>
       </c>
       <c r="B16" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2141,31 +2146,30 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2173,10 +2177,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>789331</v>
+        <v>789227</v>
       </c>
       <c r="R16" t="n">
-        <v>7151248</v>
+        <v>7151210</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2211,17 +2215,13 @@
           <t>2025-10-28</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>ringhack på tall</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2675,7 +2675,7 @@
         <v>129742631</v>
       </c>
       <c r="B21" t="n">
-        <v>91544</v>
+        <v>91548</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2992,37 +2992,42 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129742557</v>
+        <v>129745532</v>
       </c>
       <c r="B24" t="n">
-        <v>92046</v>
+        <v>57733</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1209</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3030,10 +3035,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>789298</v>
+        <v>789215</v>
       </c>
       <c r="R24" t="n">
-        <v>7151197</v>
+        <v>7151159</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3070,7 +3075,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>på samma granlåga som ullticka</t>
+          <t>hack i låga</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3079,7 +3084,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3098,42 +3102,37 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129745532</v>
+        <v>129742557</v>
       </c>
       <c r="B25" t="n">
-        <v>57733</v>
+        <v>92050</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>1209</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3141,10 +3140,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>789215</v>
+        <v>789298</v>
       </c>
       <c r="R25" t="n">
-        <v>7151159</v>
+        <v>7151197</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3181,7 +3180,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>hack i låga</t>
+          <t>på samma granlåga som ullticka</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3190,6 +3189,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3208,10 +3208,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129745551</v>
+        <v>129744135</v>
       </c>
       <c r="B26" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3219,30 +3219,31 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3250,10 +3251,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>789219</v>
+        <v>789284</v>
       </c>
       <c r="R26" t="n">
-        <v>7151168</v>
+        <v>7151167</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3288,13 +3289,17 @@
           <t>2025-10-28</t>
         </is>
       </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>äldre ringhack på gran</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3313,38 +3318,38 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129745563</v>
+        <v>129745551</v>
       </c>
       <c r="B27" t="n">
-        <v>91557</v>
+        <v>79081</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
@@ -3355,10 +3360,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>789198</v>
+        <v>789219</v>
       </c>
       <c r="R27" t="n">
-        <v>7151158</v>
+        <v>7151168</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3418,42 +3423,41 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129744135</v>
+        <v>129745563</v>
       </c>
       <c r="B28" t="n">
-        <v>57736</v>
+        <v>91561</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3461,10 +3465,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>789284</v>
+        <v>789198</v>
       </c>
       <c r="R28" t="n">
-        <v>7151167</v>
+        <v>7151158</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3499,17 +3503,13 @@
           <t>2025-10-28</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>äldre ringhack på gran</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3528,41 +3528,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129742620</v>
+        <v>129745383</v>
       </c>
       <c r="B29" t="n">
-        <v>91557</v>
+        <v>79081</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr"/>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3570,10 +3574,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>789294</v>
+        <v>789239</v>
       </c>
       <c r="R29" t="n">
-        <v>7151188</v>
+        <v>7151169</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3606,6 +3610,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>fertil</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3738,45 +3747,41 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129745383</v>
+        <v>129742620</v>
       </c>
       <c r="B31" t="n">
-        <v>79081</v>
+        <v>91561</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr">
         <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3784,10 +3789,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>789239</v>
+        <v>789294</v>
       </c>
       <c r="R31" t="n">
-        <v>7151169</v>
+        <v>7151188</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3820,11 +3825,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-10-28</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>fertil</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4172,10 +4172,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129742429</v>
+        <v>129742261</v>
       </c>
       <c r="B35" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4183,30 +4183,27 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4214,10 +4211,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>789351</v>
+        <v>789192</v>
       </c>
       <c r="R35" t="n">
-        <v>7151276</v>
+        <v>7151225</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4252,13 +4249,17 @@
           <t>2025-10-28</t>
         </is>
       </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>barksprätt på gammal gran</t>
+        </is>
+      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4280,7 +4281,7 @@
         <v>129744558</v>
       </c>
       <c r="B36" t="n">
-        <v>91593</v>
+        <v>91597</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4382,10 +4383,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129742261</v>
+        <v>129742429</v>
       </c>
       <c r="B37" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4393,27 +4394,30 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4421,10 +4425,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>789192</v>
+        <v>789351</v>
       </c>
       <c r="R37" t="n">
-        <v>7151225</v>
+        <v>7151276</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4459,17 +4463,13 @@
           <t>2025-10-28</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>barksprätt på gammal gran</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -5021,7 +5021,7 @@
         <v>129742518</v>
       </c>
       <c r="B43" t="n">
-        <v>91557</v>
+        <v>91561</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/A 50406-2025 artfynd.xlsx
+++ b/artfynd/A 50406-2025 artfynd.xlsx
@@ -1265,10 +1265,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129745889</v>
+        <v>129745363</v>
       </c>
       <c r="B8" t="n">
-        <v>82916</v>
+        <v>57733</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1276,30 +1276,31 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1312</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1307,10 +1308,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>789222</v>
+        <v>789241</v>
       </c>
       <c r="R8" t="n">
-        <v>7151172</v>
+        <v>7151185</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1345,13 +1346,17 @@
           <t>2025-10-28</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>på nära håll</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1370,10 +1375,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129745363</v>
+        <v>129745889</v>
       </c>
       <c r="B9" t="n">
-        <v>57733</v>
+        <v>82918</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1381,31 +1386,30 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>1312</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1413,10 +1417,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>789241</v>
+        <v>789222</v>
       </c>
       <c r="R9" t="n">
-        <v>7151185</v>
+        <v>7151172</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1451,17 +1455,13 @@
           <t>2025-10-28</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>på nära håll</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1480,10 +1480,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129742539</v>
+        <v>129743137</v>
       </c>
       <c r="B10" t="n">
-        <v>91597</v>
+        <v>57736</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1491,30 +1491,31 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1522,10 +1523,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>789298</v>
+        <v>789220</v>
       </c>
       <c r="R10" t="n">
-        <v>7151197</v>
+        <v>7151136</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1562,7 +1563,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>på samma låga som rynkskinn</t>
+          <t>färska ringhack som utgörs av små punkthack på en gran</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1571,7 +1572,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1590,10 +1590,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129743137</v>
+        <v>129742539</v>
       </c>
       <c r="B11" t="n">
-        <v>57736</v>
+        <v>91599</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1601,31 +1601,30 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1633,10 +1632,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>789220</v>
+        <v>789298</v>
       </c>
       <c r="R11" t="n">
-        <v>7151136</v>
+        <v>7151197</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1673,7 +1672,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>färska ringhack som utgörs av små punkthack på en gran</t>
+          <t>på samma låga som rynkskinn</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1682,6 +1681,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1700,10 +1700,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129742521</v>
+        <v>129745950</v>
       </c>
       <c r="B12" t="n">
-        <v>57736</v>
+        <v>82918</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1711,31 +1711,30 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1743,10 +1742,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>789331</v>
+        <v>789199</v>
       </c>
       <c r="R12" t="n">
-        <v>7151248</v>
+        <v>7151153</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1781,17 +1780,13 @@
           <t>2025-10-28</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>ringhack på tall</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1810,10 +1805,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129743913</v>
+        <v>129745347</v>
       </c>
       <c r="B13" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1821,31 +1816,30 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1853,10 +1847,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>789283</v>
+        <v>789248</v>
       </c>
       <c r="R13" t="n">
-        <v>7151180</v>
+        <v>7151191</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1893,7 +1887,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>ringhack på gammal gran</t>
+          <t>på stammen av en tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1902,6 +1896,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1920,10 +1915,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129745950</v>
+        <v>129745328</v>
       </c>
       <c r="B14" t="n">
-        <v>82916</v>
+        <v>79081</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1931,27 +1926,27 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -1962,10 +1957,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>789199</v>
+        <v>789227</v>
       </c>
       <c r="R14" t="n">
-        <v>7151153</v>
+        <v>7151210</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2025,10 +2020,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129745347</v>
+        <v>129743913</v>
       </c>
       <c r="B15" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2036,30 +2031,31 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2067,10 +2063,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>789248</v>
+        <v>789283</v>
       </c>
       <c r="R15" t="n">
-        <v>7151191</v>
+        <v>7151180</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2107,7 +2103,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>på stammen av en tall</t>
+          <t>ringhack på gammal gran</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2116,7 +2112,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2135,10 +2130,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129745328</v>
+        <v>129742521</v>
       </c>
       <c r="B16" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2146,30 +2141,31 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2177,10 +2173,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>789227</v>
+        <v>789331</v>
       </c>
       <c r="R16" t="n">
-        <v>7151210</v>
+        <v>7151248</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2215,13 +2211,17 @@
           <t>2025-10-28</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>ringhack på tall</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2240,10 +2240,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129746089</v>
+        <v>129745466</v>
       </c>
       <c r="B17" t="n">
-        <v>82916</v>
+        <v>57733</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2251,30 +2251,31 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1312</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2282,10 +2283,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>789203</v>
+        <v>789212</v>
       </c>
       <c r="R17" t="n">
-        <v>7151242</v>
+        <v>7151164</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2320,13 +2321,17 @@
           <t>2025-10-28</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>bohål i gran</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2345,10 +2350,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129742406</v>
+        <v>129746089</v>
       </c>
       <c r="B18" t="n">
-        <v>79081</v>
+        <v>82918</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2356,27 +2361,27 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -2387,10 +2392,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>789267</v>
+        <v>789203</v>
       </c>
       <c r="R18" t="n">
-        <v>7151238</v>
+        <v>7151242</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2450,10 +2455,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129745466</v>
+        <v>129742406</v>
       </c>
       <c r="B19" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2461,31 +2466,30 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2493,10 +2497,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>789212</v>
+        <v>789267</v>
       </c>
       <c r="R19" t="n">
-        <v>7151164</v>
+        <v>7151238</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2531,17 +2535,13 @@
           <t>2025-10-28</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>bohål i gran</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2672,10 +2672,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129742631</v>
+        <v>129745993</v>
       </c>
       <c r="B21" t="n">
-        <v>91548</v>
+        <v>79081</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2683,27 +2683,27 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>112</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -2714,10 +2714,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>789289</v>
+        <v>789196</v>
       </c>
       <c r="R21" t="n">
-        <v>7151198</v>
+        <v>7151151</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2750,6 +2750,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>ca 70cm lång bål!</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2777,10 +2782,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129745993</v>
+        <v>129742631</v>
       </c>
       <c r="B22" t="n">
-        <v>79081</v>
+        <v>91550</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2788,27 +2793,27 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>112</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -2819,10 +2824,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>789196</v>
+        <v>789289</v>
       </c>
       <c r="R22" t="n">
-        <v>7151151</v>
+        <v>7151198</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2855,11 +2860,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-28</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>ca 70cm lång bål!</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3105,7 +3105,7 @@
         <v>129742557</v>
       </c>
       <c r="B25" t="n">
-        <v>92050</v>
+        <v>92052</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3208,10 +3208,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129744135</v>
+        <v>129745551</v>
       </c>
       <c r="B26" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3219,31 +3219,30 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3251,10 +3250,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>789284</v>
+        <v>789219</v>
       </c>
       <c r="R26" t="n">
-        <v>7151167</v>
+        <v>7151168</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3289,17 +3288,13 @@
           <t>2025-10-28</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>äldre ringhack på gran</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3318,38 +3313,38 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129745551</v>
+        <v>129745563</v>
       </c>
       <c r="B27" t="n">
-        <v>79081</v>
+        <v>91563</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
@@ -3360,10 +3355,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>789219</v>
+        <v>789198</v>
       </c>
       <c r="R27" t="n">
-        <v>7151168</v>
+        <v>7151158</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3423,41 +3418,42 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129745563</v>
+        <v>129744135</v>
       </c>
       <c r="B28" t="n">
-        <v>91561</v>
+        <v>57736</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3465,10 +3461,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>789198</v>
+        <v>789284</v>
       </c>
       <c r="R28" t="n">
-        <v>7151158</v>
+        <v>7151167</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3503,13 +3499,17 @@
           <t>2025-10-28</t>
         </is>
       </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>äldre ringhack på gran</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3750,7 +3750,7 @@
         <v>129742620</v>
       </c>
       <c r="B31" t="n">
-        <v>91561</v>
+        <v>91563</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4172,10 +4172,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129742261</v>
+        <v>129744558</v>
       </c>
       <c r="B35" t="n">
-        <v>57736</v>
+        <v>91599</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4183,27 +4183,30 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4211,10 +4214,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>789192</v>
+        <v>789368</v>
       </c>
       <c r="R35" t="n">
-        <v>7151225</v>
+        <v>7151214</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4249,17 +4252,13 @@
           <t>2025-10-28</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>barksprätt på gammal gran</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4278,10 +4277,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129744558</v>
+        <v>129742429</v>
       </c>
       <c r="B36" t="n">
-        <v>91597</v>
+        <v>79081</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4289,27 +4288,27 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
@@ -4320,10 +4319,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>789368</v>
+        <v>789351</v>
       </c>
       <c r="R36" t="n">
-        <v>7151214</v>
+        <v>7151276</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4383,10 +4382,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129742429</v>
+        <v>129742261</v>
       </c>
       <c r="B37" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4394,30 +4393,27 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4425,10 +4421,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>789351</v>
+        <v>789192</v>
       </c>
       <c r="R37" t="n">
-        <v>7151276</v>
+        <v>7151225</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4463,13 +4459,17 @@
           <t>2025-10-28</t>
         </is>
       </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>barksprätt på gammal gran</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4706,7 +4706,7 @@
         <v>129745946</v>
       </c>
       <c r="B40" t="n">
-        <v>82916</v>
+        <v>82918</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5021,7 +5021,7 @@
         <v>129742518</v>
       </c>
       <c r="B43" t="n">
-        <v>91561</v>
+        <v>91563</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/A 50406-2025 artfynd.xlsx
+++ b/artfynd/A 50406-2025 artfynd.xlsx
@@ -1480,10 +1480,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129743137</v>
+        <v>129742539</v>
       </c>
       <c r="B10" t="n">
-        <v>57736</v>
+        <v>91599</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1491,31 +1491,30 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1523,10 +1522,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>789220</v>
+        <v>789298</v>
       </c>
       <c r="R10" t="n">
-        <v>7151136</v>
+        <v>7151197</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1563,7 +1562,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>färska ringhack som utgörs av små punkthack på en gran</t>
+          <t>på samma låga som rynkskinn</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1572,6 +1571,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1590,10 +1590,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129742539</v>
+        <v>129743137</v>
       </c>
       <c r="B11" t="n">
-        <v>91599</v>
+        <v>57736</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1601,30 +1601,31 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1632,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>789298</v>
+        <v>789220</v>
       </c>
       <c r="R11" t="n">
-        <v>7151197</v>
+        <v>7151136</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1672,7 +1673,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>på samma låga som rynkskinn</t>
+          <t>färska ringhack som utgörs av små punkthack på en gran</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1681,7 +1682,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -2992,42 +2992,37 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129745532</v>
+        <v>129742557</v>
       </c>
       <c r="B24" t="n">
-        <v>57733</v>
+        <v>92052</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>1209</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3035,10 +3030,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>789215</v>
+        <v>789298</v>
       </c>
       <c r="R24" t="n">
-        <v>7151159</v>
+        <v>7151197</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3075,7 +3070,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>hack i låga</t>
+          <t>på samma granlåga som ullticka</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3084,6 +3079,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3102,37 +3098,42 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129742557</v>
+        <v>129745532</v>
       </c>
       <c r="B25" t="n">
-        <v>92052</v>
+        <v>57733</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1209</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3140,10 +3141,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>789298</v>
+        <v>789215</v>
       </c>
       <c r="R25" t="n">
-        <v>7151197</v>
+        <v>7151159</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3180,7 +3181,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>på samma granlåga som ullticka</t>
+          <t>hack i låga</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3189,7 +3190,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3313,41 +3313,42 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129745563</v>
+        <v>129744135</v>
       </c>
       <c r="B27" t="n">
-        <v>91563</v>
+        <v>57736</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3355,10 +3356,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>789198</v>
+        <v>789284</v>
       </c>
       <c r="R27" t="n">
-        <v>7151158</v>
+        <v>7151167</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3393,13 +3394,17 @@
           <t>2025-10-28</t>
         </is>
       </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>äldre ringhack på gran</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3418,42 +3423,41 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129744135</v>
+        <v>129745563</v>
       </c>
       <c r="B28" t="n">
-        <v>57736</v>
+        <v>91563</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3461,10 +3465,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>789284</v>
+        <v>789198</v>
       </c>
       <c r="R28" t="n">
-        <v>7151167</v>
+        <v>7151158</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3499,17 +3503,13 @@
           <t>2025-10-28</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>äldre ringhack på gran</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -4913,38 +4913,38 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129742516</v>
+        <v>129742518</v>
       </c>
       <c r="B42" t="n">
-        <v>79081</v>
+        <v>91563</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K42" t="inlineStr"/>
@@ -4955,10 +4955,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>789348</v>
+        <v>789345</v>
       </c>
       <c r="R42" t="n">
-        <v>7151255</v>
+        <v>7151261</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5018,38 +5018,38 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129742518</v>
+        <v>129742516</v>
       </c>
       <c r="B43" t="n">
-        <v>91563</v>
+        <v>79081</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K43" t="inlineStr"/>
@@ -5060,10 +5060,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>789345</v>
+        <v>789348</v>
       </c>
       <c r="R43" t="n">
-        <v>7151261</v>
+        <v>7151255</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>

--- a/artfynd/A 50406-2025 artfynd.xlsx
+++ b/artfynd/A 50406-2025 artfynd.xlsx
@@ -1480,10 +1480,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129742539</v>
+        <v>129743137</v>
       </c>
       <c r="B10" t="n">
-        <v>91599</v>
+        <v>57736</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1491,30 +1491,31 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1522,10 +1523,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>789298</v>
+        <v>789220</v>
       </c>
       <c r="R10" t="n">
-        <v>7151197</v>
+        <v>7151136</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1562,7 +1563,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>på samma låga som rynkskinn</t>
+          <t>färska ringhack som utgörs av små punkthack på en gran</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1571,7 +1572,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1590,10 +1590,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129743137</v>
+        <v>129742539</v>
       </c>
       <c r="B11" t="n">
-        <v>57736</v>
+        <v>91599</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1601,31 +1601,30 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1633,10 +1632,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>789220</v>
+        <v>789298</v>
       </c>
       <c r="R11" t="n">
-        <v>7151136</v>
+        <v>7151197</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1673,7 +1672,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>färska ringhack som utgörs av små punkthack på en gran</t>
+          <t>på samma låga som rynkskinn</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1682,6 +1681,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1700,10 +1700,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129745950</v>
+        <v>129743913</v>
       </c>
       <c r="B12" t="n">
-        <v>82918</v>
+        <v>57736</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1711,30 +1711,31 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1742,10 +1743,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>789199</v>
+        <v>789283</v>
       </c>
       <c r="R12" t="n">
-        <v>7151153</v>
+        <v>7151180</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1780,13 +1781,17 @@
           <t>2025-10-28</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>ringhack på gammal gran</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1805,10 +1810,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129745347</v>
+        <v>129742521</v>
       </c>
       <c r="B13" t="n">
-        <v>79081</v>
+        <v>57736</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1816,30 +1821,31 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1847,10 +1853,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>789248</v>
+        <v>789331</v>
       </c>
       <c r="R13" t="n">
-        <v>7151191</v>
+        <v>7151248</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1887,7 +1893,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>på stammen av en tall</t>
+          <t>ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1896,7 +1902,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1915,10 +1920,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129745328</v>
+        <v>129745950</v>
       </c>
       <c r="B14" t="n">
-        <v>79081</v>
+        <v>82918</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1926,27 +1931,27 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -1957,10 +1962,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>789227</v>
+        <v>789199</v>
       </c>
       <c r="R14" t="n">
-        <v>7151210</v>
+        <v>7151153</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2020,10 +2025,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129743913</v>
+        <v>129745347</v>
       </c>
       <c r="B15" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2031,31 +2036,30 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2063,10 +2067,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>789283</v>
+        <v>789248</v>
       </c>
       <c r="R15" t="n">
-        <v>7151180</v>
+        <v>7151191</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2103,7 +2107,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>ringhack på gammal gran</t>
+          <t>på stammen av en tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2112,6 +2116,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2130,10 +2135,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129742521</v>
+        <v>129745328</v>
       </c>
       <c r="B16" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2141,31 +2146,30 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2173,10 +2177,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>789331</v>
+        <v>789227</v>
       </c>
       <c r="R16" t="n">
-        <v>7151248</v>
+        <v>7151210</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2211,17 +2215,13 @@
           <t>2025-10-28</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>ringhack på tall</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2672,10 +2672,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129745993</v>
+        <v>129742631</v>
       </c>
       <c r="B21" t="n">
-        <v>79081</v>
+        <v>91550</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2683,27 +2683,27 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>112</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -2714,10 +2714,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>789196</v>
+        <v>789289</v>
       </c>
       <c r="R21" t="n">
-        <v>7151151</v>
+        <v>7151198</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2750,11 +2750,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-10-28</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>ca 70cm lång bål!</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2782,10 +2777,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129742631</v>
+        <v>129745993</v>
       </c>
       <c r="B22" t="n">
-        <v>91550</v>
+        <v>79081</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2793,27 +2788,27 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>112</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -2824,10 +2819,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>789289</v>
+        <v>789196</v>
       </c>
       <c r="R22" t="n">
-        <v>7151198</v>
+        <v>7151151</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2860,6 +2855,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>ca 70cm lång bål!</t>
         </is>
       </c>
       <c r="AD22" t="b">

--- a/artfynd/A 50406-2025 artfynd.xlsx
+++ b/artfynd/A 50406-2025 artfynd.xlsx
@@ -2672,10 +2672,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129742631</v>
+        <v>129745993</v>
       </c>
       <c r="B21" t="n">
-        <v>91550</v>
+        <v>79081</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2683,27 +2683,27 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>112</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -2714,10 +2714,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>789289</v>
+        <v>789196</v>
       </c>
       <c r="R21" t="n">
-        <v>7151198</v>
+        <v>7151151</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2750,6 +2750,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>ca 70cm lång bål!</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2777,10 +2782,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129745993</v>
+        <v>129742631</v>
       </c>
       <c r="B22" t="n">
-        <v>79081</v>
+        <v>91550</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2788,27 +2793,27 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>112</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -2819,10 +2824,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>789196</v>
+        <v>789289</v>
       </c>
       <c r="R22" t="n">
-        <v>7151151</v>
+        <v>7151198</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2855,11 +2860,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-28</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>ca 70cm lång bål!</t>
         </is>
       </c>
       <c r="AD22" t="b">

--- a/artfynd/A 50406-2025 artfynd.xlsx
+++ b/artfynd/A 50406-2025 artfynd.xlsx
@@ -1265,10 +1265,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129745363</v>
+        <v>129745889</v>
       </c>
       <c r="B8" t="n">
-        <v>57733</v>
+        <v>82918</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1276,31 +1276,30 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>1312</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1308,10 +1307,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>789241</v>
+        <v>789222</v>
       </c>
       <c r="R8" t="n">
-        <v>7151185</v>
+        <v>7151172</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1346,17 +1345,13 @@
           <t>2025-10-28</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>på nära håll</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1375,10 +1370,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129745889</v>
+        <v>129745363</v>
       </c>
       <c r="B9" t="n">
-        <v>82918</v>
+        <v>57733</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1386,30 +1381,31 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1312</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1417,10 +1413,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>789222</v>
+        <v>789241</v>
       </c>
       <c r="R9" t="n">
-        <v>7151172</v>
+        <v>7151185</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1455,13 +1451,17 @@
           <t>2025-10-28</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>på nära håll</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1480,10 +1480,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129743137</v>
+        <v>129742539</v>
       </c>
       <c r="B10" t="n">
-        <v>57736</v>
+        <v>91599</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1491,31 +1491,30 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1523,10 +1522,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>789220</v>
+        <v>789298</v>
       </c>
       <c r="R10" t="n">
-        <v>7151136</v>
+        <v>7151197</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1563,7 +1562,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>färska ringhack som utgörs av små punkthack på en gran</t>
+          <t>på samma låga som rynkskinn</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1572,6 +1571,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1590,10 +1590,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129742539</v>
+        <v>129743137</v>
       </c>
       <c r="B11" t="n">
-        <v>91599</v>
+        <v>57736</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1601,30 +1601,31 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1632,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>789298</v>
+        <v>789220</v>
       </c>
       <c r="R11" t="n">
-        <v>7151197</v>
+        <v>7151136</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1672,7 +1673,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>på samma låga som rynkskinn</t>
+          <t>färska ringhack som utgörs av små punkthack på en gran</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1681,7 +1682,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -2240,10 +2240,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129745466</v>
+        <v>129746089</v>
       </c>
       <c r="B17" t="n">
-        <v>57733</v>
+        <v>82918</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2251,31 +2251,30 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>1312</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2283,10 +2282,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>789212</v>
+        <v>789203</v>
       </c>
       <c r="R17" t="n">
-        <v>7151164</v>
+        <v>7151242</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2321,17 +2320,13 @@
           <t>2025-10-28</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>bohål i gran</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2350,10 +2345,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129746089</v>
+        <v>129742406</v>
       </c>
       <c r="B18" t="n">
-        <v>82918</v>
+        <v>79081</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2361,27 +2356,27 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -2392,10 +2387,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>789203</v>
+        <v>789267</v>
       </c>
       <c r="R18" t="n">
-        <v>7151242</v>
+        <v>7151238</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2455,10 +2450,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129742406</v>
+        <v>129745466</v>
       </c>
       <c r="B19" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2466,30 +2461,31 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2497,10 +2493,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>789267</v>
+        <v>789212</v>
       </c>
       <c r="R19" t="n">
-        <v>7151238</v>
+        <v>7151164</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2535,13 +2531,17 @@
           <t>2025-10-28</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>bohål i gran</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2672,10 +2672,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129745993</v>
+        <v>129742631</v>
       </c>
       <c r="B21" t="n">
-        <v>79081</v>
+        <v>91550</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2683,27 +2683,27 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>112</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -2714,10 +2714,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>789196</v>
+        <v>789289</v>
       </c>
       <c r="R21" t="n">
-        <v>7151151</v>
+        <v>7151198</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2750,11 +2750,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-10-28</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>ca 70cm lång bål!</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2782,10 +2777,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129742631</v>
+        <v>129745993</v>
       </c>
       <c r="B22" t="n">
-        <v>91550</v>
+        <v>79081</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2793,27 +2788,27 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>112</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -2824,10 +2819,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>789289</v>
+        <v>789196</v>
       </c>
       <c r="R22" t="n">
-        <v>7151198</v>
+        <v>7151151</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2860,6 +2855,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>ca 70cm lång bål!</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3208,38 +3208,38 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129745551</v>
+        <v>129745563</v>
       </c>
       <c r="B26" t="n">
-        <v>79081</v>
+        <v>91563</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
@@ -3250,10 +3250,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>789219</v>
+        <v>789198</v>
       </c>
       <c r="R26" t="n">
-        <v>7151168</v>
+        <v>7151158</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3313,10 +3313,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129744135</v>
+        <v>129745551</v>
       </c>
       <c r="B27" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3324,31 +3324,30 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3356,10 +3355,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>789284</v>
+        <v>789219</v>
       </c>
       <c r="R27" t="n">
-        <v>7151167</v>
+        <v>7151168</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3394,17 +3393,13 @@
           <t>2025-10-28</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>äldre ringhack på gran</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3423,41 +3418,42 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129745563</v>
+        <v>129744135</v>
       </c>
       <c r="B28" t="n">
-        <v>91563</v>
+        <v>57736</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3465,10 +3461,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>789198</v>
+        <v>789284</v>
       </c>
       <c r="R28" t="n">
-        <v>7151158</v>
+        <v>7151167</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3503,13 +3499,17 @@
           <t>2025-10-28</t>
         </is>
       </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>äldre ringhack på gran</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3528,45 +3528,41 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129745383</v>
+        <v>129742620</v>
       </c>
       <c r="B29" t="n">
-        <v>79081</v>
+        <v>91563</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3574,10 +3570,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>789239</v>
+        <v>789294</v>
       </c>
       <c r="R29" t="n">
-        <v>7151169</v>
+        <v>7151188</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3610,11 +3606,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-10-28</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>fertil</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3642,7 +3633,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129745427</v>
+        <v>129745383</v>
       </c>
       <c r="B30" t="n">
         <v>79081</v>
@@ -3676,7 +3667,11 @@
           <t>bålar</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3684,7 +3679,7 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>789221</v>
+        <v>789239</v>
       </c>
       <c r="R30" t="n">
         <v>7151169</v>
@@ -3720,6 +3715,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>fertil</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3747,38 +3747,38 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129742620</v>
+        <v>129745427</v>
       </c>
       <c r="B31" t="n">
-        <v>91563</v>
+        <v>79081</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
@@ -3789,10 +3789,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>789294</v>
+        <v>789221</v>
       </c>
       <c r="R31" t="n">
-        <v>7151188</v>
+        <v>7151169</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4703,10 +4703,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129745946</v>
+        <v>129745167</v>
       </c>
       <c r="B40" t="n">
-        <v>82918</v>
+        <v>79081</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4714,27 +4714,27 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
@@ -4745,10 +4745,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>789208</v>
+        <v>789233</v>
       </c>
       <c r="R40" t="n">
-        <v>7151157</v>
+        <v>7151272</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4808,10 +4808,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129745167</v>
+        <v>129745946</v>
       </c>
       <c r="B41" t="n">
-        <v>79081</v>
+        <v>82918</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4819,27 +4819,27 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
@@ -4850,10 +4850,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>789233</v>
+        <v>789208</v>
       </c>
       <c r="R41" t="n">
-        <v>7151272</v>
+        <v>7151157</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>

--- a/artfynd/A 50406-2025 artfynd.xlsx
+++ b/artfynd/A 50406-2025 artfynd.xlsx
@@ -1480,10 +1480,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129742539</v>
+        <v>129743137</v>
       </c>
       <c r="B10" t="n">
-        <v>91599</v>
+        <v>57736</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1491,30 +1491,31 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1522,10 +1523,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>789298</v>
+        <v>789220</v>
       </c>
       <c r="R10" t="n">
-        <v>7151197</v>
+        <v>7151136</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1562,7 +1563,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>på samma låga som rynkskinn</t>
+          <t>färska ringhack som utgörs av små punkthack på en gran</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1571,7 +1572,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1590,10 +1590,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129743137</v>
+        <v>129742539</v>
       </c>
       <c r="B11" t="n">
-        <v>57736</v>
+        <v>91599</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1601,31 +1601,30 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1633,10 +1632,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>789220</v>
+        <v>789298</v>
       </c>
       <c r="R11" t="n">
-        <v>7151136</v>
+        <v>7151197</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1673,7 +1672,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>färska ringhack som utgörs av små punkthack på en gran</t>
+          <t>på samma låga som rynkskinn</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1682,6 +1681,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -2240,10 +2240,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129746089</v>
+        <v>129742406</v>
       </c>
       <c r="B17" t="n">
-        <v>82918</v>
+        <v>79081</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2251,27 +2251,27 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -2282,10 +2282,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>789203</v>
+        <v>789267</v>
       </c>
       <c r="R17" t="n">
-        <v>7151242</v>
+        <v>7151238</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2345,10 +2345,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129742406</v>
+        <v>129746089</v>
       </c>
       <c r="B18" t="n">
-        <v>79081</v>
+        <v>82918</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2356,27 +2356,27 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -2387,10 +2387,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>789267</v>
+        <v>789203</v>
       </c>
       <c r="R18" t="n">
-        <v>7151238</v>
+        <v>7151242</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -3852,10 +3852,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129745155</v>
+        <v>129742300</v>
       </c>
       <c r="B32" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3863,30 +3863,31 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -3894,10 +3895,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>789288</v>
+        <v>789197</v>
       </c>
       <c r="R32" t="n">
-        <v>7151234</v>
+        <v>7151175</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3932,13 +3933,17 @@
           <t>2025-10-28</t>
         </is>
       </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>hål i tall</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -3957,10 +3962,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129742300</v>
+        <v>129745155</v>
       </c>
       <c r="B33" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3968,31 +3973,30 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4000,10 +4004,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>789197</v>
+        <v>789288</v>
       </c>
       <c r="R33" t="n">
-        <v>7151175</v>
+        <v>7151234</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4038,17 +4042,13 @@
           <t>2025-10-28</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>hål i tall</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4172,10 +4172,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129744558</v>
+        <v>129742429</v>
       </c>
       <c r="B35" t="n">
-        <v>91599</v>
+        <v>79081</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4183,27 +4183,27 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
@@ -4214,10 +4214,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>789368</v>
+        <v>789351</v>
       </c>
       <c r="R35" t="n">
-        <v>7151214</v>
+        <v>7151276</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4277,10 +4277,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129742429</v>
+        <v>129744558</v>
       </c>
       <c r="B36" t="n">
-        <v>79081</v>
+        <v>91599</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4288,27 +4288,27 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
@@ -4319,10 +4319,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>789351</v>
+        <v>789368</v>
       </c>
       <c r="R36" t="n">
-        <v>7151276</v>
+        <v>7151214</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>

--- a/artfynd/A 50406-2025 artfynd.xlsx
+++ b/artfynd/A 50406-2025 artfynd.xlsx
@@ -1163,7 +1163,7 @@
         <v>129742487</v>
       </c>
       <c r="B7" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>129745889</v>
       </c>
       <c r="B8" t="n">
-        <v>82918</v>
+        <v>82921</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1373,7 +1373,7 @@
         <v>129745363</v>
       </c>
       <c r="B9" t="n">
-        <v>57733</v>
+        <v>57734</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1480,10 +1480,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129743137</v>
+        <v>129742539</v>
       </c>
       <c r="B10" t="n">
-        <v>57736</v>
+        <v>91602</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1491,31 +1491,30 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1523,10 +1522,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>789220</v>
+        <v>789298</v>
       </c>
       <c r="R10" t="n">
-        <v>7151136</v>
+        <v>7151197</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1563,7 +1562,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>färska ringhack som utgörs av små punkthack på en gran</t>
+          <t>på samma låga som rynkskinn</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1572,6 +1571,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1590,10 +1590,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129742539</v>
+        <v>129743137</v>
       </c>
       <c r="B11" t="n">
-        <v>91599</v>
+        <v>57737</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1601,30 +1601,31 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1632,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>789298</v>
+        <v>789220</v>
       </c>
       <c r="R11" t="n">
-        <v>7151197</v>
+        <v>7151136</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1672,7 +1673,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>på samma låga som rynkskinn</t>
+          <t>färska ringhack som utgörs av små punkthack på en gran</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1681,7 +1682,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1700,10 +1700,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129743913</v>
+        <v>129745950</v>
       </c>
       <c r="B12" t="n">
-        <v>57736</v>
+        <v>82921</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1711,31 +1711,30 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1743,10 +1742,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>789283</v>
+        <v>789199</v>
       </c>
       <c r="R12" t="n">
-        <v>7151180</v>
+        <v>7151153</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1781,17 +1780,13 @@
           <t>2025-10-28</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>ringhack på gammal gran</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1813,7 +1808,7 @@
         <v>129742521</v>
       </c>
       <c r="B13" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1920,10 +1915,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129745950</v>
+        <v>129743913</v>
       </c>
       <c r="B14" t="n">
-        <v>82918</v>
+        <v>57737</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1931,30 +1926,31 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -1962,10 +1958,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>789199</v>
+        <v>789283</v>
       </c>
       <c r="R14" t="n">
-        <v>7151153</v>
+        <v>7151180</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2000,13 +1996,17 @@
           <t>2025-10-28</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>ringhack på gammal gran</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2028,7 +2028,7 @@
         <v>129745347</v>
       </c>
       <c r="B15" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2138,7 +2138,7 @@
         <v>129745328</v>
       </c>
       <c r="B16" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2240,10 +2240,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129742406</v>
+        <v>129746089</v>
       </c>
       <c r="B17" t="n">
-        <v>79081</v>
+        <v>82921</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2251,27 +2251,27 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -2282,10 +2282,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>789267</v>
+        <v>789203</v>
       </c>
       <c r="R17" t="n">
-        <v>7151238</v>
+        <v>7151242</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2345,10 +2345,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129746089</v>
+        <v>129742406</v>
       </c>
       <c r="B18" t="n">
-        <v>82918</v>
+        <v>79084</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2356,27 +2356,27 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -2387,10 +2387,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>789203</v>
+        <v>789267</v>
       </c>
       <c r="R18" t="n">
-        <v>7151242</v>
+        <v>7151238</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2453,7 +2453,7 @@
         <v>129745466</v>
       </c>
       <c r="B19" t="n">
-        <v>57733</v>
+        <v>57734</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2675,7 +2675,7 @@
         <v>129742631</v>
       </c>
       <c r="B21" t="n">
-        <v>91550</v>
+        <v>91553</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2780,7 +2780,7 @@
         <v>129745993</v>
       </c>
       <c r="B22" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2890,7 +2890,7 @@
         <v>129745192</v>
       </c>
       <c r="B23" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2992,37 +2992,42 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129742557</v>
+        <v>129745532</v>
       </c>
       <c r="B24" t="n">
-        <v>92052</v>
+        <v>57734</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1209</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3030,10 +3035,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>789298</v>
+        <v>789215</v>
       </c>
       <c r="R24" t="n">
-        <v>7151197</v>
+        <v>7151159</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3070,7 +3075,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>på samma granlåga som ullticka</t>
+          <t>hack i låga</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3079,7 +3084,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3098,42 +3102,37 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129745532</v>
+        <v>129742557</v>
       </c>
       <c r="B25" t="n">
-        <v>57733</v>
+        <v>92055</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>1209</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3141,10 +3140,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>789215</v>
+        <v>789298</v>
       </c>
       <c r="R25" t="n">
-        <v>7151159</v>
+        <v>7151197</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3181,7 +3180,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>hack i låga</t>
+          <t>på samma granlåga som ullticka</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3190,6 +3189,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3208,38 +3208,38 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129745563</v>
+        <v>129745551</v>
       </c>
       <c r="B26" t="n">
-        <v>91563</v>
+        <v>79084</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
@@ -3250,10 +3250,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>789198</v>
+        <v>789219</v>
       </c>
       <c r="R26" t="n">
-        <v>7151158</v>
+        <v>7151168</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3313,10 +3313,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129745551</v>
+        <v>129744135</v>
       </c>
       <c r="B27" t="n">
-        <v>79081</v>
+        <v>57737</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3324,30 +3324,31 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3355,10 +3356,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>789219</v>
+        <v>789284</v>
       </c>
       <c r="R27" t="n">
-        <v>7151168</v>
+        <v>7151167</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3393,13 +3394,17 @@
           <t>2025-10-28</t>
         </is>
       </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>äldre ringhack på gran</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3418,42 +3423,41 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129744135</v>
+        <v>129745563</v>
       </c>
       <c r="B28" t="n">
-        <v>57736</v>
+        <v>91566</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3461,10 +3465,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>789284</v>
+        <v>789198</v>
       </c>
       <c r="R28" t="n">
-        <v>7151167</v>
+        <v>7151158</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3499,17 +3503,13 @@
           <t>2025-10-28</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>äldre ringhack på gran</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3528,41 +3528,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129742620</v>
+        <v>129745383</v>
       </c>
       <c r="B29" t="n">
-        <v>91563</v>
+        <v>79084</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr"/>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3570,10 +3574,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>789294</v>
+        <v>789239</v>
       </c>
       <c r="R29" t="n">
-        <v>7151188</v>
+        <v>7151169</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3606,6 +3610,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>fertil</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3633,10 +3642,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129745383</v>
+        <v>129745427</v>
       </c>
       <c r="B30" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3667,11 +3676,7 @@
           <t>bålar</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3679,7 +3684,7 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>789239</v>
+        <v>789221</v>
       </c>
       <c r="R30" t="n">
         <v>7151169</v>
@@ -3715,11 +3720,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-10-28</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>fertil</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3747,38 +3747,38 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129745427</v>
+        <v>129742620</v>
       </c>
       <c r="B31" t="n">
-        <v>79081</v>
+        <v>91566</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
@@ -3789,10 +3789,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>789221</v>
+        <v>789294</v>
       </c>
       <c r="R31" t="n">
-        <v>7151169</v>
+        <v>7151188</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3855,7 +3855,7 @@
         <v>129742300</v>
       </c>
       <c r="B32" t="n">
-        <v>57733</v>
+        <v>57734</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3965,7 +3965,7 @@
         <v>129745155</v>
       </c>
       <c r="B33" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4070,7 +4070,7 @@
         <v>129742254</v>
       </c>
       <c r="B34" t="n">
-        <v>79113</v>
+        <v>79116</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4172,10 +4172,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129742429</v>
+        <v>129744558</v>
       </c>
       <c r="B35" t="n">
-        <v>79081</v>
+        <v>91602</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4183,27 +4183,27 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
@@ -4214,10 +4214,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>789351</v>
+        <v>789368</v>
       </c>
       <c r="R35" t="n">
-        <v>7151276</v>
+        <v>7151214</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4277,10 +4277,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129744558</v>
+        <v>129742429</v>
       </c>
       <c r="B36" t="n">
-        <v>91599</v>
+        <v>79084</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4288,27 +4288,27 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
@@ -4319,10 +4319,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>789368</v>
+        <v>789351</v>
       </c>
       <c r="R36" t="n">
-        <v>7151214</v>
+        <v>7151276</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4385,7 +4385,7 @@
         <v>129742261</v>
       </c>
       <c r="B37" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4491,7 +4491,7 @@
         <v>129742447</v>
       </c>
       <c r="B38" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4601,7 +4601,7 @@
         <v>129745159</v>
       </c>
       <c r="B39" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4706,7 +4706,7 @@
         <v>129745167</v>
       </c>
       <c r="B40" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4811,7 +4811,7 @@
         <v>129745946</v>
       </c>
       <c r="B41" t="n">
-        <v>82918</v>
+        <v>82921</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4916,7 +4916,7 @@
         <v>129742518</v>
       </c>
       <c r="B42" t="n">
-        <v>91563</v>
+        <v>91566</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5021,7 +5021,7 @@
         <v>129742516</v>
       </c>
       <c r="B43" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5126,7 +5126,7 @@
         <v>129825892</v>
       </c>
       <c r="B44" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>

--- a/artfynd/A 50406-2025 artfynd.xlsx
+++ b/artfynd/A 50406-2025 artfynd.xlsx
@@ -1700,10 +1700,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129745950</v>
+        <v>129745347</v>
       </c>
       <c r="B12" t="n">
-        <v>82921</v>
+        <v>79084</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1711,27 +1711,27 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1742,10 +1742,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>789199</v>
+        <v>789248</v>
       </c>
       <c r="R12" t="n">
-        <v>7151153</v>
+        <v>7151191</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1778,6 +1778,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>på stammen av en tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1805,10 +1810,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129742521</v>
+        <v>129745328</v>
       </c>
       <c r="B13" t="n">
-        <v>57737</v>
+        <v>79084</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1816,31 +1821,30 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1848,10 +1852,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>789331</v>
+        <v>789227</v>
       </c>
       <c r="R13" t="n">
-        <v>7151248</v>
+        <v>7151210</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1886,17 +1890,13 @@
           <t>2025-10-28</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>ringhack på tall</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1915,7 +1915,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129743913</v>
+        <v>129742521</v>
       </c>
       <c r="B14" t="n">
         <v>57737</v>
@@ -1948,7 +1948,7 @@
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -1958,10 +1958,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>789283</v>
+        <v>789331</v>
       </c>
       <c r="R14" t="n">
-        <v>7151180</v>
+        <v>7151248</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1998,7 +1998,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>ringhack på gammal gran</t>
+          <t>ringhack på tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2025,10 +2025,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129745347</v>
+        <v>129743913</v>
       </c>
       <c r="B15" t="n">
-        <v>79084</v>
+        <v>57737</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2036,30 +2036,31 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2067,10 +2068,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>789248</v>
+        <v>789283</v>
       </c>
       <c r="R15" t="n">
-        <v>7151191</v>
+        <v>7151180</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2107,7 +2108,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>på stammen av en tall</t>
+          <t>ringhack på gammal gran</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2116,7 +2117,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2135,10 +2135,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129745328</v>
+        <v>129745950</v>
       </c>
       <c r="B16" t="n">
-        <v>79084</v>
+        <v>82921</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2146,27 +2146,27 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -2177,10 +2177,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>789227</v>
+        <v>789199</v>
       </c>
       <c r="R16" t="n">
-        <v>7151210</v>
+        <v>7151153</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2240,10 +2240,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129746089</v>
+        <v>129742406</v>
       </c>
       <c r="B17" t="n">
-        <v>82921</v>
+        <v>79084</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2251,27 +2251,27 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -2282,10 +2282,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>789203</v>
+        <v>789267</v>
       </c>
       <c r="R17" t="n">
-        <v>7151242</v>
+        <v>7151238</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2345,10 +2345,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129742406</v>
+        <v>129746089</v>
       </c>
       <c r="B18" t="n">
-        <v>79084</v>
+        <v>82921</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2356,27 +2356,27 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -2387,10 +2387,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>789267</v>
+        <v>789203</v>
       </c>
       <c r="R18" t="n">
-        <v>7151238</v>
+        <v>7151242</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2992,42 +2992,37 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129745532</v>
+        <v>129742557</v>
       </c>
       <c r="B24" t="n">
-        <v>57734</v>
+        <v>92055</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>1209</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3035,10 +3030,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>789215</v>
+        <v>789298</v>
       </c>
       <c r="R24" t="n">
-        <v>7151159</v>
+        <v>7151197</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3075,7 +3070,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>hack i låga</t>
+          <t>på samma granlåga som ullticka</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3084,6 +3079,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3102,37 +3098,42 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129742557</v>
+        <v>129745532</v>
       </c>
       <c r="B25" t="n">
-        <v>92055</v>
+        <v>57734</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1209</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3140,10 +3141,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>789298</v>
+        <v>789215</v>
       </c>
       <c r="R25" t="n">
-        <v>7151197</v>
+        <v>7151159</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3180,7 +3181,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>på samma granlåga som ullticka</t>
+          <t>hack i låga</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3189,7 +3190,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3313,42 +3313,41 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129744135</v>
+        <v>129745563</v>
       </c>
       <c r="B27" t="n">
-        <v>57737</v>
+        <v>91566</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3356,10 +3355,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>789284</v>
+        <v>789198</v>
       </c>
       <c r="R27" t="n">
-        <v>7151167</v>
+        <v>7151158</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3394,17 +3393,13 @@
           <t>2025-10-28</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>äldre ringhack på gran</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3423,41 +3418,42 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129745563</v>
+        <v>129744135</v>
       </c>
       <c r="B28" t="n">
-        <v>91566</v>
+        <v>57737</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3465,10 +3461,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>789198</v>
+        <v>789284</v>
       </c>
       <c r="R28" t="n">
-        <v>7151158</v>
+        <v>7151167</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3503,13 +3499,17 @@
           <t>2025-10-28</t>
         </is>
       </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>äldre ringhack på gran</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -4277,10 +4277,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129742429</v>
+        <v>129742261</v>
       </c>
       <c r="B36" t="n">
-        <v>79084</v>
+        <v>57737</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4288,30 +4288,27 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4319,10 +4316,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>789351</v>
+        <v>789192</v>
       </c>
       <c r="R36" t="n">
-        <v>7151276</v>
+        <v>7151225</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4357,13 +4354,17 @@
           <t>2025-10-28</t>
         </is>
       </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>barksprätt på gammal gran</t>
+        </is>
+      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4382,10 +4383,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129742261</v>
+        <v>129742429</v>
       </c>
       <c r="B37" t="n">
-        <v>57737</v>
+        <v>79084</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4393,27 +4394,30 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4421,10 +4425,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>789192</v>
+        <v>789351</v>
       </c>
       <c r="R37" t="n">
-        <v>7151225</v>
+        <v>7151276</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4459,17 +4463,13 @@
           <t>2025-10-28</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>barksprätt på gammal gran</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4703,10 +4703,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129745167</v>
+        <v>129745946</v>
       </c>
       <c r="B40" t="n">
-        <v>79084</v>
+        <v>82921</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4714,27 +4714,27 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
@@ -4745,10 +4745,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>789233</v>
+        <v>789208</v>
       </c>
       <c r="R40" t="n">
-        <v>7151272</v>
+        <v>7151157</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4808,10 +4808,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129745946</v>
+        <v>129745167</v>
       </c>
       <c r="B41" t="n">
-        <v>82921</v>
+        <v>79084</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4819,27 +4819,27 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
@@ -4850,10 +4850,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>789208</v>
+        <v>789233</v>
       </c>
       <c r="R41" t="n">
-        <v>7151157</v>
+        <v>7151272</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4913,38 +4913,38 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129742518</v>
+        <v>129742516</v>
       </c>
       <c r="B42" t="n">
-        <v>91566</v>
+        <v>79084</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K42" t="inlineStr"/>
@@ -4955,10 +4955,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>789345</v>
+        <v>789348</v>
       </c>
       <c r="R42" t="n">
-        <v>7151261</v>
+        <v>7151255</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5018,38 +5018,38 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129742516</v>
+        <v>129742518</v>
       </c>
       <c r="B43" t="n">
-        <v>79084</v>
+        <v>91566</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K43" t="inlineStr"/>
@@ -5060,10 +5060,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>789348</v>
+        <v>789345</v>
       </c>
       <c r="R43" t="n">
-        <v>7151255</v>
+        <v>7151261</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>

--- a/artfynd/A 50406-2025 artfynd.xlsx
+++ b/artfynd/A 50406-2025 artfynd.xlsx
@@ -1265,10 +1265,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129745889</v>
+        <v>129745363</v>
       </c>
       <c r="B8" t="n">
-        <v>82921</v>
+        <v>57734</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1276,30 +1276,31 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1312</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1307,10 +1308,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>789222</v>
+        <v>789241</v>
       </c>
       <c r="R8" t="n">
-        <v>7151172</v>
+        <v>7151185</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1345,13 +1346,17 @@
           <t>2025-10-28</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>på nära håll</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1370,10 +1375,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129745363</v>
+        <v>129745889</v>
       </c>
       <c r="B9" t="n">
-        <v>57734</v>
+        <v>82921</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1381,31 +1386,30 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>1312</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1413,10 +1417,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>789241</v>
+        <v>789222</v>
       </c>
       <c r="R9" t="n">
-        <v>7151185</v>
+        <v>7151172</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1451,17 +1455,13 @@
           <t>2025-10-28</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>på nära håll</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1700,10 +1700,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129745347</v>
+        <v>129745950</v>
       </c>
       <c r="B12" t="n">
-        <v>79084</v>
+        <v>82921</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1711,27 +1711,27 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1742,10 +1742,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>789248</v>
+        <v>789199</v>
       </c>
       <c r="R12" t="n">
-        <v>7151191</v>
+        <v>7151153</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1778,11 +1778,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-28</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>på stammen av en tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1810,7 +1805,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129745328</v>
+        <v>129745347</v>
       </c>
       <c r="B13" t="n">
         <v>79084</v>
@@ -1852,10 +1847,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>789227</v>
+        <v>789248</v>
       </c>
       <c r="R13" t="n">
-        <v>7151210</v>
+        <v>7151191</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1888,6 +1883,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>på stammen av en tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1915,10 +1915,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129742521</v>
+        <v>129745328</v>
       </c>
       <c r="B14" t="n">
-        <v>57737</v>
+        <v>79084</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1926,31 +1926,30 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -1958,10 +1957,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>789331</v>
+        <v>789227</v>
       </c>
       <c r="R14" t="n">
-        <v>7151248</v>
+        <v>7151210</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1996,17 +1995,13 @@
           <t>2025-10-28</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>ringhack på tall</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2025,7 +2020,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129743913</v>
+        <v>129742521</v>
       </c>
       <c r="B15" t="n">
         <v>57737</v>
@@ -2058,7 +2053,7 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -2068,10 +2063,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>789283</v>
+        <v>789331</v>
       </c>
       <c r="R15" t="n">
-        <v>7151180</v>
+        <v>7151248</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2108,7 +2103,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>ringhack på gammal gran</t>
+          <t>ringhack på tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2135,10 +2130,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129745950</v>
+        <v>129743913</v>
       </c>
       <c r="B16" t="n">
-        <v>82921</v>
+        <v>57737</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2146,30 +2141,31 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2177,10 +2173,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>789199</v>
+        <v>789283</v>
       </c>
       <c r="R16" t="n">
-        <v>7151153</v>
+        <v>7151180</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2215,13 +2211,17 @@
           <t>2025-10-28</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>ringhack på gammal gran</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -3852,10 +3852,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129742300</v>
+        <v>129745155</v>
       </c>
       <c r="B32" t="n">
-        <v>57734</v>
+        <v>79084</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3863,31 +3863,30 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -3895,10 +3894,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>789197</v>
+        <v>789288</v>
       </c>
       <c r="R32" t="n">
-        <v>7151175</v>
+        <v>7151234</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3933,17 +3932,13 @@
           <t>2025-10-28</t>
         </is>
       </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>hål i tall</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -3962,10 +3957,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129745155</v>
+        <v>129742300</v>
       </c>
       <c r="B33" t="n">
-        <v>79084</v>
+        <v>57734</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3973,30 +3968,31 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4004,10 +4000,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>789288</v>
+        <v>789197</v>
       </c>
       <c r="R33" t="n">
-        <v>7151234</v>
+        <v>7151175</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4042,13 +4038,17 @@
           <t>2025-10-28</t>
         </is>
       </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>hål i tall</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4172,10 +4172,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129744558</v>
+        <v>129742261</v>
       </c>
       <c r="B35" t="n">
-        <v>91602</v>
+        <v>57737</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4183,30 +4183,27 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4214,10 +4211,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>789368</v>
+        <v>789192</v>
       </c>
       <c r="R35" t="n">
-        <v>7151214</v>
+        <v>7151225</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4252,13 +4249,17 @@
           <t>2025-10-28</t>
         </is>
       </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>barksprätt på gammal gran</t>
+        </is>
+      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4277,10 +4278,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129742261</v>
+        <v>129744558</v>
       </c>
       <c r="B36" t="n">
-        <v>57737</v>
+        <v>91602</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4288,27 +4289,30 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4316,10 +4320,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>789192</v>
+        <v>789368</v>
       </c>
       <c r="R36" t="n">
-        <v>7151225</v>
+        <v>7151214</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4354,17 +4358,13 @@
           <t>2025-10-28</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>barksprätt på gammal gran</t>
-        </is>
-      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 50406-2025 artfynd.xlsx
+++ b/artfynd/A 50406-2025 artfynd.xlsx
@@ -1163,7 +1163,7 @@
         <v>129742487</v>
       </c>
       <c r="B7" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1265,10 +1265,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129745363</v>
+        <v>129745889</v>
       </c>
       <c r="B8" t="n">
-        <v>57734</v>
+        <v>82924</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1276,31 +1276,30 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>1312</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1308,10 +1307,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>789241</v>
+        <v>789222</v>
       </c>
       <c r="R8" t="n">
-        <v>7151185</v>
+        <v>7151172</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1346,17 +1345,13 @@
           <t>2025-10-28</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>på nära håll</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1375,10 +1370,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129745889</v>
+        <v>129745363</v>
       </c>
       <c r="B9" t="n">
-        <v>82921</v>
+        <v>57737</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1386,30 +1381,31 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1312</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1417,10 +1413,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>789222</v>
+        <v>789241</v>
       </c>
       <c r="R9" t="n">
-        <v>7151172</v>
+        <v>7151185</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1455,13 +1451,17 @@
           <t>2025-10-28</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>på nära håll</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1483,7 +1483,7 @@
         <v>129742539</v>
       </c>
       <c r="B10" t="n">
-        <v>91602</v>
+        <v>91605</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         <v>129743137</v>
       </c>
       <c r="B11" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>129745950</v>
       </c>
       <c r="B12" t="n">
-        <v>82921</v>
+        <v>82924</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,10 +1805,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129745347</v>
+        <v>129743913</v>
       </c>
       <c r="B13" t="n">
-        <v>79084</v>
+        <v>57740</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1816,30 +1816,31 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1847,10 +1848,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>789248</v>
+        <v>789283</v>
       </c>
       <c r="R13" t="n">
-        <v>7151191</v>
+        <v>7151180</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1887,7 +1888,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>på stammen av en tall</t>
+          <t>ringhack på gammal gran</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1896,7 +1897,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1915,10 +1915,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129745328</v>
+        <v>129742521</v>
       </c>
       <c r="B14" t="n">
-        <v>79084</v>
+        <v>57740</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1926,30 +1926,31 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -1957,10 +1958,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>789227</v>
+        <v>789331</v>
       </c>
       <c r="R14" t="n">
-        <v>7151210</v>
+        <v>7151248</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1995,13 +1996,17 @@
           <t>2025-10-28</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>ringhack på tall</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2020,10 +2025,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129742521</v>
+        <v>129745347</v>
       </c>
       <c r="B15" t="n">
-        <v>57737</v>
+        <v>79087</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2031,31 +2036,30 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2063,10 +2067,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>789331</v>
+        <v>789248</v>
       </c>
       <c r="R15" t="n">
-        <v>7151248</v>
+        <v>7151191</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2103,7 +2107,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>ringhack på tall</t>
+          <t>på stammen av en tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2112,6 +2116,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2130,10 +2135,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129743913</v>
+        <v>129745328</v>
       </c>
       <c r="B16" t="n">
-        <v>57737</v>
+        <v>79087</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2141,31 +2146,30 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2173,10 +2177,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>789283</v>
+        <v>789227</v>
       </c>
       <c r="R16" t="n">
-        <v>7151180</v>
+        <v>7151210</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2211,17 +2215,13 @@
           <t>2025-10-28</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>ringhack på gammal gran</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2240,10 +2240,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129742406</v>
+        <v>129746089</v>
       </c>
       <c r="B17" t="n">
-        <v>79084</v>
+        <v>82924</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2251,27 +2251,27 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -2282,10 +2282,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>789267</v>
+        <v>789203</v>
       </c>
       <c r="R17" t="n">
-        <v>7151238</v>
+        <v>7151242</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2345,10 +2345,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129746089</v>
+        <v>129742406</v>
       </c>
       <c r="B18" t="n">
-        <v>82921</v>
+        <v>79087</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2356,27 +2356,27 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -2387,10 +2387,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>789203</v>
+        <v>789267</v>
       </c>
       <c r="R18" t="n">
-        <v>7151242</v>
+        <v>7151238</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2453,7 +2453,7 @@
         <v>129745466</v>
       </c>
       <c r="B19" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2675,7 +2675,7 @@
         <v>129742631</v>
       </c>
       <c r="B21" t="n">
-        <v>91553</v>
+        <v>91556</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2780,7 +2780,7 @@
         <v>129745993</v>
       </c>
       <c r="B22" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2890,7 +2890,7 @@
         <v>129745192</v>
       </c>
       <c r="B23" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2995,7 +2995,7 @@
         <v>129742557</v>
       </c>
       <c r="B24" t="n">
-        <v>92055</v>
+        <v>92058</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3101,7 +3101,7 @@
         <v>129745532</v>
       </c>
       <c r="B25" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3211,7 +3211,7 @@
         <v>129745551</v>
       </c>
       <c r="B26" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3313,41 +3313,42 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129745563</v>
+        <v>129744135</v>
       </c>
       <c r="B27" t="n">
-        <v>91566</v>
+        <v>57740</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3355,10 +3356,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>789198</v>
+        <v>789284</v>
       </c>
       <c r="R27" t="n">
-        <v>7151158</v>
+        <v>7151167</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3393,13 +3394,17 @@
           <t>2025-10-28</t>
         </is>
       </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>äldre ringhack på gran</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3418,42 +3423,41 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129744135</v>
+        <v>129745563</v>
       </c>
       <c r="B28" t="n">
-        <v>57737</v>
+        <v>91569</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3461,10 +3465,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>789284</v>
+        <v>789198</v>
       </c>
       <c r="R28" t="n">
-        <v>7151167</v>
+        <v>7151158</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3499,17 +3503,13 @@
           <t>2025-10-28</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>äldre ringhack på gran</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3528,45 +3528,41 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129745383</v>
+        <v>129742620</v>
       </c>
       <c r="B29" t="n">
-        <v>79084</v>
+        <v>91569</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3574,10 +3570,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>789239</v>
+        <v>789294</v>
       </c>
       <c r="R29" t="n">
-        <v>7151169</v>
+        <v>7151188</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3610,11 +3606,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-10-28</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>fertil</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3642,10 +3633,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129745427</v>
+        <v>129745383</v>
       </c>
       <c r="B30" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3676,7 +3667,11 @@
           <t>bålar</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3684,7 +3679,7 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>789221</v>
+        <v>789239</v>
       </c>
       <c r="R30" t="n">
         <v>7151169</v>
@@ -3720,6 +3715,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>fertil</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3747,38 +3747,38 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129742620</v>
+        <v>129745427</v>
       </c>
       <c r="B31" t="n">
-        <v>91566</v>
+        <v>79087</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
@@ -3789,10 +3789,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>789294</v>
+        <v>789221</v>
       </c>
       <c r="R31" t="n">
-        <v>7151188</v>
+        <v>7151169</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3855,7 +3855,7 @@
         <v>129745155</v>
       </c>
       <c r="B32" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3960,7 +3960,7 @@
         <v>129742300</v>
       </c>
       <c r="B33" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4070,7 +4070,7 @@
         <v>129742254</v>
       </c>
       <c r="B34" t="n">
-        <v>79116</v>
+        <v>79119</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4172,10 +4172,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129742261</v>
+        <v>129742429</v>
       </c>
       <c r="B35" t="n">
-        <v>57737</v>
+        <v>79087</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4183,27 +4183,30 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4211,10 +4214,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>789192</v>
+        <v>789351</v>
       </c>
       <c r="R35" t="n">
-        <v>7151225</v>
+        <v>7151276</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4249,17 +4252,13 @@
           <t>2025-10-28</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>barksprätt på gammal gran</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4281,7 +4280,7 @@
         <v>129744558</v>
       </c>
       <c r="B36" t="n">
-        <v>91602</v>
+        <v>91605</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4383,10 +4382,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129742429</v>
+        <v>129742261</v>
       </c>
       <c r="B37" t="n">
-        <v>79084</v>
+        <v>57740</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4394,30 +4393,27 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4425,10 +4421,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>789351</v>
+        <v>789192</v>
       </c>
       <c r="R37" t="n">
-        <v>7151276</v>
+        <v>7151225</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4463,13 +4459,17 @@
           <t>2025-10-28</t>
         </is>
       </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>barksprätt på gammal gran</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4491,7 +4491,7 @@
         <v>129742447</v>
       </c>
       <c r="B38" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4601,7 +4601,7 @@
         <v>129745159</v>
       </c>
       <c r="B39" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4706,7 +4706,7 @@
         <v>129745946</v>
       </c>
       <c r="B40" t="n">
-        <v>82921</v>
+        <v>82924</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4811,7 +4811,7 @@
         <v>129745167</v>
       </c>
       <c r="B41" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4916,7 +4916,7 @@
         <v>129742516</v>
       </c>
       <c r="B42" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5021,7 +5021,7 @@
         <v>129742518</v>
       </c>
       <c r="B43" t="n">
-        <v>91566</v>
+        <v>91569</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5126,7 +5126,7 @@
         <v>129825892</v>
       </c>
       <c r="B44" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>

--- a/artfynd/A 50406-2025 artfynd.xlsx
+++ b/artfynd/A 50406-2025 artfynd.xlsx
@@ -1805,10 +1805,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129743913</v>
+        <v>129745347</v>
       </c>
       <c r="B13" t="n">
-        <v>57740</v>
+        <v>79087</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1816,31 +1816,30 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1848,10 +1847,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>789283</v>
+        <v>789248</v>
       </c>
       <c r="R13" t="n">
-        <v>7151180</v>
+        <v>7151191</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1888,7 +1887,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>ringhack på gammal gran</t>
+          <t>på stammen av en tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1897,6 +1896,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1915,10 +1915,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129742521</v>
+        <v>129745328</v>
       </c>
       <c r="B14" t="n">
-        <v>57740</v>
+        <v>79087</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1926,31 +1926,30 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -1958,10 +1957,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>789331</v>
+        <v>789227</v>
       </c>
       <c r="R14" t="n">
-        <v>7151248</v>
+        <v>7151210</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1996,17 +1995,13 @@
           <t>2025-10-28</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>ringhack på tall</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2025,10 +2020,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129745347</v>
+        <v>129743913</v>
       </c>
       <c r="B15" t="n">
-        <v>79087</v>
+        <v>57740</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2036,30 +2031,31 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2067,10 +2063,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>789248</v>
+        <v>789283</v>
       </c>
       <c r="R15" t="n">
-        <v>7151191</v>
+        <v>7151180</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2107,7 +2103,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>på stammen av en tall</t>
+          <t>ringhack på gammal gran</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2116,7 +2112,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2135,10 +2130,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129745328</v>
+        <v>129742521</v>
       </c>
       <c r="B16" t="n">
-        <v>79087</v>
+        <v>57740</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2146,30 +2141,31 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2177,10 +2173,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>789227</v>
+        <v>789331</v>
       </c>
       <c r="R16" t="n">
-        <v>7151210</v>
+        <v>7151248</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2215,13 +2211,17 @@
           <t>2025-10-28</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>ringhack på tall</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2240,10 +2240,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129746089</v>
+        <v>129742406</v>
       </c>
       <c r="B17" t="n">
-        <v>82924</v>
+        <v>79087</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2251,27 +2251,27 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -2282,10 +2282,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>789203</v>
+        <v>789267</v>
       </c>
       <c r="R17" t="n">
-        <v>7151242</v>
+        <v>7151238</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2345,10 +2345,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129742406</v>
+        <v>129745466</v>
       </c>
       <c r="B18" t="n">
-        <v>79087</v>
+        <v>57737</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2356,30 +2356,31 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2387,10 +2388,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>789267</v>
+        <v>789212</v>
       </c>
       <c r="R18" t="n">
-        <v>7151238</v>
+        <v>7151164</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2425,13 +2426,17 @@
           <t>2025-10-28</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>bohål i gran</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2450,10 +2455,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129745466</v>
+        <v>129746089</v>
       </c>
       <c r="B19" t="n">
-        <v>57737</v>
+        <v>82924</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2461,31 +2466,30 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>1312</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2493,10 +2497,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>789212</v>
+        <v>789203</v>
       </c>
       <c r="R19" t="n">
-        <v>7151164</v>
+        <v>7151242</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2531,17 +2535,13 @@
           <t>2025-10-28</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>bohål i gran</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2992,37 +2992,42 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129742557</v>
+        <v>129745532</v>
       </c>
       <c r="B24" t="n">
-        <v>92058</v>
+        <v>57737</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1209</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3030,10 +3035,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>789298</v>
+        <v>789215</v>
       </c>
       <c r="R24" t="n">
-        <v>7151197</v>
+        <v>7151159</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3070,7 +3075,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>på samma granlåga som ullticka</t>
+          <t>hack i låga</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3079,7 +3084,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3098,42 +3102,37 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129745532</v>
+        <v>129742557</v>
       </c>
       <c r="B25" t="n">
-        <v>57737</v>
+        <v>92058</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>1209</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3141,10 +3140,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>789215</v>
+        <v>789298</v>
       </c>
       <c r="R25" t="n">
-        <v>7151159</v>
+        <v>7151197</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3181,7 +3180,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>hack i låga</t>
+          <t>på samma granlåga som ullticka</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3190,6 +3189,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -4172,10 +4172,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129742429</v>
+        <v>129744558</v>
       </c>
       <c r="B35" t="n">
-        <v>79087</v>
+        <v>91605</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4183,27 +4183,27 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
@@ -4214,10 +4214,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>789351</v>
+        <v>789368</v>
       </c>
       <c r="R35" t="n">
-        <v>7151276</v>
+        <v>7151214</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4277,10 +4277,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129744558</v>
+        <v>129742429</v>
       </c>
       <c r="B36" t="n">
-        <v>91605</v>
+        <v>79087</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4288,27 +4288,27 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
@@ -4319,10 +4319,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>789368</v>
+        <v>789351</v>
       </c>
       <c r="R36" t="n">
-        <v>7151214</v>
+        <v>7151276</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4703,10 +4703,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129745946</v>
+        <v>129745167</v>
       </c>
       <c r="B40" t="n">
-        <v>82924</v>
+        <v>79087</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4714,27 +4714,27 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
@@ -4745,10 +4745,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>789208</v>
+        <v>789233</v>
       </c>
       <c r="R40" t="n">
-        <v>7151157</v>
+        <v>7151272</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4808,10 +4808,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129745167</v>
+        <v>129745946</v>
       </c>
       <c r="B41" t="n">
-        <v>79087</v>
+        <v>82924</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4819,27 +4819,27 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
@@ -4850,10 +4850,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>789233</v>
+        <v>789208</v>
       </c>
       <c r="R41" t="n">
-        <v>7151272</v>
+        <v>7151157</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4913,38 +4913,38 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129742516</v>
+        <v>129742518</v>
       </c>
       <c r="B42" t="n">
-        <v>79087</v>
+        <v>91569</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K42" t="inlineStr"/>
@@ -4955,10 +4955,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>789348</v>
+        <v>789345</v>
       </c>
       <c r="R42" t="n">
-        <v>7151255</v>
+        <v>7151261</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5018,38 +5018,38 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129742518</v>
+        <v>129742516</v>
       </c>
       <c r="B43" t="n">
-        <v>91569</v>
+        <v>79087</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K43" t="inlineStr"/>
@@ -5060,10 +5060,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>789345</v>
+        <v>789348</v>
       </c>
       <c r="R43" t="n">
-        <v>7151261</v>
+        <v>7151255</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>

--- a/artfynd/A 50406-2025 artfynd.xlsx
+++ b/artfynd/A 50406-2025 artfynd.xlsx
@@ -2672,10 +2672,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129742631</v>
+        <v>129745993</v>
       </c>
       <c r="B21" t="n">
-        <v>91556</v>
+        <v>79087</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2683,27 +2683,27 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>112</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -2714,10 +2714,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>789289</v>
+        <v>789196</v>
       </c>
       <c r="R21" t="n">
-        <v>7151198</v>
+        <v>7151151</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2750,6 +2750,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>ca 70cm lång bål!</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2777,10 +2782,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129745993</v>
+        <v>129742631</v>
       </c>
       <c r="B22" t="n">
-        <v>79087</v>
+        <v>91556</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2788,27 +2793,27 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>112</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -2819,10 +2824,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>789196</v>
+        <v>789289</v>
       </c>
       <c r="R22" t="n">
-        <v>7151151</v>
+        <v>7151198</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2855,11 +2860,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-28</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>ca 70cm lång bål!</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3208,38 +3208,38 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129745551</v>
+        <v>129745563</v>
       </c>
       <c r="B26" t="n">
-        <v>79087</v>
+        <v>91569</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
@@ -3250,10 +3250,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>789219</v>
+        <v>789198</v>
       </c>
       <c r="R26" t="n">
-        <v>7151168</v>
+        <v>7151158</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3313,10 +3313,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129744135</v>
+        <v>129745551</v>
       </c>
       <c r="B27" t="n">
-        <v>57740</v>
+        <v>79087</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3324,31 +3324,30 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3356,10 +3355,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>789284</v>
+        <v>789219</v>
       </c>
       <c r="R27" t="n">
-        <v>7151167</v>
+        <v>7151168</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3394,17 +3393,13 @@
           <t>2025-10-28</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>äldre ringhack på gran</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3423,41 +3418,42 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129745563</v>
+        <v>129744135</v>
       </c>
       <c r="B28" t="n">
-        <v>91569</v>
+        <v>57740</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3465,10 +3461,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>789198</v>
+        <v>789284</v>
       </c>
       <c r="R28" t="n">
-        <v>7151158</v>
+        <v>7151167</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3503,13 +3499,17 @@
           <t>2025-10-28</t>
         </is>
       </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>äldre ringhack på gran</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -4172,10 +4172,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129744558</v>
+        <v>129742429</v>
       </c>
       <c r="B35" t="n">
-        <v>91605</v>
+        <v>79087</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4183,27 +4183,27 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
@@ -4214,10 +4214,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>789368</v>
+        <v>789351</v>
       </c>
       <c r="R35" t="n">
-        <v>7151214</v>
+        <v>7151276</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4277,10 +4277,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129742429</v>
+        <v>129744558</v>
       </c>
       <c r="B36" t="n">
-        <v>79087</v>
+        <v>91605</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4288,27 +4288,27 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
@@ -4319,10 +4319,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>789351</v>
+        <v>789368</v>
       </c>
       <c r="R36" t="n">
-        <v>7151276</v>
+        <v>7151214</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4703,10 +4703,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129745167</v>
+        <v>129745946</v>
       </c>
       <c r="B40" t="n">
-        <v>79087</v>
+        <v>82924</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4714,27 +4714,27 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
@@ -4745,10 +4745,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>789233</v>
+        <v>789208</v>
       </c>
       <c r="R40" t="n">
-        <v>7151272</v>
+        <v>7151157</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4808,10 +4808,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129745946</v>
+        <v>129745167</v>
       </c>
       <c r="B41" t="n">
-        <v>82924</v>
+        <v>79087</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4819,27 +4819,27 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
@@ -4850,10 +4850,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>789208</v>
+        <v>789233</v>
       </c>
       <c r="R41" t="n">
-        <v>7151157</v>
+        <v>7151272</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>

--- a/artfynd/A 50406-2025 artfynd.xlsx
+++ b/artfynd/A 50406-2025 artfynd.xlsx
@@ -1163,7 +1163,7 @@
         <v>129742487</v>
       </c>
       <c r="B7" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>129745889</v>
       </c>
       <c r="B8" t="n">
-        <v>82924</v>
+        <v>82925</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1483,7 +1483,7 @@
         <v>129742539</v>
       </c>
       <c r="B10" t="n">
-        <v>91605</v>
+        <v>91606</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1700,10 +1700,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129745950</v>
+        <v>129743913</v>
       </c>
       <c r="B12" t="n">
-        <v>82924</v>
+        <v>57740</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1711,30 +1711,31 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1742,10 +1743,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>789199</v>
+        <v>789283</v>
       </c>
       <c r="R12" t="n">
-        <v>7151153</v>
+        <v>7151180</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1780,13 +1781,17 @@
           <t>2025-10-28</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>ringhack på gammal gran</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1805,10 +1810,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129745347</v>
+        <v>129742521</v>
       </c>
       <c r="B13" t="n">
-        <v>79087</v>
+        <v>57740</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1816,30 +1821,31 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1847,10 +1853,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>789248</v>
+        <v>789331</v>
       </c>
       <c r="R13" t="n">
-        <v>7151191</v>
+        <v>7151248</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1887,7 +1893,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>på stammen av en tall</t>
+          <t>ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1896,7 +1902,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1915,10 +1920,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129745328</v>
+        <v>129745950</v>
       </c>
       <c r="B14" t="n">
-        <v>79087</v>
+        <v>82925</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1926,27 +1931,27 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -1957,10 +1962,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>789227</v>
+        <v>789199</v>
       </c>
       <c r="R14" t="n">
-        <v>7151210</v>
+        <v>7151153</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2020,10 +2025,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129743913</v>
+        <v>129745347</v>
       </c>
       <c r="B15" t="n">
-        <v>57740</v>
+        <v>79088</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2031,31 +2036,30 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2063,10 +2067,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>789283</v>
+        <v>789248</v>
       </c>
       <c r="R15" t="n">
-        <v>7151180</v>
+        <v>7151191</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2103,7 +2107,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>ringhack på gammal gran</t>
+          <t>på stammen av en tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2112,6 +2116,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2130,10 +2135,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129742521</v>
+        <v>129745328</v>
       </c>
       <c r="B16" t="n">
-        <v>57740</v>
+        <v>79088</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2141,31 +2146,30 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2173,10 +2177,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>789331</v>
+        <v>789227</v>
       </c>
       <c r="R16" t="n">
-        <v>7151248</v>
+        <v>7151210</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2211,17 +2215,13 @@
           <t>2025-10-28</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>ringhack på tall</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2240,10 +2240,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129742406</v>
+        <v>129746089</v>
       </c>
       <c r="B17" t="n">
-        <v>79087</v>
+        <v>82925</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2251,27 +2251,27 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -2282,10 +2282,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>789267</v>
+        <v>789203</v>
       </c>
       <c r="R17" t="n">
-        <v>7151238</v>
+        <v>7151242</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2345,10 +2345,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129745466</v>
+        <v>129742406</v>
       </c>
       <c r="B18" t="n">
-        <v>57737</v>
+        <v>79088</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2356,31 +2356,30 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2388,10 +2387,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>789212</v>
+        <v>789267</v>
       </c>
       <c r="R18" t="n">
-        <v>7151164</v>
+        <v>7151238</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2426,17 +2425,13 @@
           <t>2025-10-28</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>bohål i gran</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2455,10 +2450,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129746089</v>
+        <v>129745466</v>
       </c>
       <c r="B19" t="n">
-        <v>82924</v>
+        <v>57737</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2466,30 +2461,31 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1312</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2497,10 +2493,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>789203</v>
+        <v>789212</v>
       </c>
       <c r="R19" t="n">
-        <v>7151242</v>
+        <v>7151164</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2535,13 +2531,17 @@
           <t>2025-10-28</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>bohål i gran</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2672,10 +2672,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129745993</v>
+        <v>129742631</v>
       </c>
       <c r="B21" t="n">
-        <v>79087</v>
+        <v>91557</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2683,27 +2683,27 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>112</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -2714,10 +2714,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>789196</v>
+        <v>789289</v>
       </c>
       <c r="R21" t="n">
-        <v>7151151</v>
+        <v>7151198</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2750,11 +2750,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-10-28</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>ca 70cm lång bål!</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2782,10 +2777,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129742631</v>
+        <v>129745993</v>
       </c>
       <c r="B22" t="n">
-        <v>91556</v>
+        <v>79088</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2793,27 +2788,27 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>112</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -2824,10 +2819,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>789289</v>
+        <v>789196</v>
       </c>
       <c r="R22" t="n">
-        <v>7151198</v>
+        <v>7151151</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2860,6 +2855,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>ca 70cm lång bål!</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2890,7 +2890,7 @@
         <v>129745192</v>
       </c>
       <c r="B23" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3105,7 +3105,7 @@
         <v>129742557</v>
       </c>
       <c r="B25" t="n">
-        <v>92058</v>
+        <v>92059</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3211,7 +3211,7 @@
         <v>129745563</v>
       </c>
       <c r="B26" t="n">
-        <v>91569</v>
+        <v>91570</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129745551</v>
+        <v>129744135</v>
       </c>
       <c r="B27" t="n">
-        <v>79087</v>
+        <v>57740</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3324,30 +3324,31 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3355,10 +3356,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>789219</v>
+        <v>789284</v>
       </c>
       <c r="R27" t="n">
-        <v>7151168</v>
+        <v>7151167</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3393,13 +3394,17 @@
           <t>2025-10-28</t>
         </is>
       </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>äldre ringhack på gran</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3418,10 +3423,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129744135</v>
+        <v>129745551</v>
       </c>
       <c r="B28" t="n">
-        <v>57740</v>
+        <v>79088</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3429,31 +3434,30 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3461,10 +3465,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>789284</v>
+        <v>789219</v>
       </c>
       <c r="R28" t="n">
-        <v>7151167</v>
+        <v>7151168</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3499,17 +3503,13 @@
           <t>2025-10-28</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>äldre ringhack på gran</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3528,41 +3528,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129742620</v>
+        <v>129745383</v>
       </c>
       <c r="B29" t="n">
-        <v>91569</v>
+        <v>79088</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr"/>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3570,10 +3574,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>789294</v>
+        <v>789239</v>
       </c>
       <c r="R29" t="n">
-        <v>7151188</v>
+        <v>7151169</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3606,6 +3610,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>fertil</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3633,10 +3642,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129745383</v>
+        <v>129745427</v>
       </c>
       <c r="B30" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3667,11 +3676,7 @@
           <t>bålar</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3679,7 +3684,7 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>789239</v>
+        <v>789221</v>
       </c>
       <c r="R30" t="n">
         <v>7151169</v>
@@ -3715,11 +3720,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-10-28</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>fertil</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3747,38 +3747,38 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129745427</v>
+        <v>129742620</v>
       </c>
       <c r="B31" t="n">
-        <v>79087</v>
+        <v>91570</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
@@ -3789,10 +3789,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>789221</v>
+        <v>789294</v>
       </c>
       <c r="R31" t="n">
-        <v>7151169</v>
+        <v>7151188</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3855,7 +3855,7 @@
         <v>129745155</v>
       </c>
       <c r="B32" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4070,7 +4070,7 @@
         <v>129742254</v>
       </c>
       <c r="B34" t="n">
-        <v>79119</v>
+        <v>79120</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4172,10 +4172,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129742429</v>
+        <v>129742261</v>
       </c>
       <c r="B35" t="n">
-        <v>79087</v>
+        <v>57740</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4183,30 +4183,27 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4214,10 +4211,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>789351</v>
+        <v>789192</v>
       </c>
       <c r="R35" t="n">
-        <v>7151276</v>
+        <v>7151225</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4252,13 +4249,17 @@
           <t>2025-10-28</t>
         </is>
       </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>barksprätt på gammal gran</t>
+        </is>
+      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4280,7 +4281,7 @@
         <v>129744558</v>
       </c>
       <c r="B36" t="n">
-        <v>91605</v>
+        <v>91606</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4382,10 +4383,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129742261</v>
+        <v>129742429</v>
       </c>
       <c r="B37" t="n">
-        <v>57740</v>
+        <v>79088</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4393,27 +4394,30 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4421,10 +4425,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>789192</v>
+        <v>789351</v>
       </c>
       <c r="R37" t="n">
-        <v>7151225</v>
+        <v>7151276</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4459,17 +4463,13 @@
           <t>2025-10-28</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>barksprätt på gammal gran</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4491,7 +4491,7 @@
         <v>129742447</v>
       </c>
       <c r="B38" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4601,7 +4601,7 @@
         <v>129745159</v>
       </c>
       <c r="B39" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4703,10 +4703,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129745946</v>
+        <v>129745167</v>
       </c>
       <c r="B40" t="n">
-        <v>82924</v>
+        <v>79088</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4714,27 +4714,27 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
@@ -4745,10 +4745,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>789208</v>
+        <v>789233</v>
       </c>
       <c r="R40" t="n">
-        <v>7151157</v>
+        <v>7151272</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4808,10 +4808,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129745167</v>
+        <v>129745946</v>
       </c>
       <c r="B41" t="n">
-        <v>79087</v>
+        <v>82925</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4819,27 +4819,27 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
@@ -4850,10 +4850,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>789233</v>
+        <v>789208</v>
       </c>
       <c r="R41" t="n">
-        <v>7151272</v>
+        <v>7151157</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4913,38 +4913,38 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129742518</v>
+        <v>129742516</v>
       </c>
       <c r="B42" t="n">
-        <v>91569</v>
+        <v>79088</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K42" t="inlineStr"/>
@@ -4955,10 +4955,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>789345</v>
+        <v>789348</v>
       </c>
       <c r="R42" t="n">
-        <v>7151261</v>
+        <v>7151255</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5018,38 +5018,38 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129742516</v>
+        <v>129742518</v>
       </c>
       <c r="B43" t="n">
-        <v>79087</v>
+        <v>91570</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K43" t="inlineStr"/>
@@ -5060,10 +5060,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>789348</v>
+        <v>789345</v>
       </c>
       <c r="R43" t="n">
-        <v>7151255</v>
+        <v>7151261</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>

--- a/artfynd/A 50406-2025 artfynd.xlsx
+++ b/artfynd/A 50406-2025 artfynd.xlsx
@@ -1480,10 +1480,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129742539</v>
+        <v>129743137</v>
       </c>
       <c r="B10" t="n">
-        <v>91606</v>
+        <v>57740</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1491,30 +1491,31 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1522,10 +1523,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>789298</v>
+        <v>789220</v>
       </c>
       <c r="R10" t="n">
-        <v>7151197</v>
+        <v>7151136</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1562,7 +1563,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>på samma låga som rynkskinn</t>
+          <t>färska ringhack som utgörs av små punkthack på en gran</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1571,7 +1572,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1590,10 +1590,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129743137</v>
+        <v>129742539</v>
       </c>
       <c r="B11" t="n">
-        <v>57740</v>
+        <v>91606</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1601,31 +1601,30 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1633,10 +1632,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>789220</v>
+        <v>789298</v>
       </c>
       <c r="R11" t="n">
-        <v>7151136</v>
+        <v>7151197</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1673,7 +1672,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>färska ringhack som utgörs av små punkthack på en gran</t>
+          <t>på samma låga som rynkskinn</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1682,6 +1681,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 50406-2025 artfynd.xlsx
+++ b/artfynd/A 50406-2025 artfynd.xlsx
@@ -1163,7 +1163,7 @@
         <v>129742487</v>
       </c>
       <c r="B7" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1265,10 +1265,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129745889</v>
+        <v>129745363</v>
       </c>
       <c r="B8" t="n">
-        <v>82925</v>
+        <v>57737</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1276,30 +1276,31 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1312</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1307,10 +1308,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>789222</v>
+        <v>789241</v>
       </c>
       <c r="R8" t="n">
-        <v>7151172</v>
+        <v>7151185</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1345,13 +1346,17 @@
           <t>2025-10-28</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>på nära håll</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1370,10 +1375,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129745363</v>
+        <v>129745889</v>
       </c>
       <c r="B9" t="n">
-        <v>57737</v>
+        <v>82931</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1381,31 +1386,30 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>1312</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1413,10 +1417,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>789241</v>
+        <v>789222</v>
       </c>
       <c r="R9" t="n">
-        <v>7151185</v>
+        <v>7151172</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1451,17 +1455,13 @@
           <t>2025-10-28</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>på nära håll</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1593,7 +1593,7 @@
         <v>129742539</v>
       </c>
       <c r="B11" t="n">
-        <v>91606</v>
+        <v>91623</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1700,10 +1700,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129743913</v>
+        <v>129745950</v>
       </c>
       <c r="B12" t="n">
-        <v>57740</v>
+        <v>82931</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1711,31 +1711,30 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1743,10 +1742,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>789283</v>
+        <v>789199</v>
       </c>
       <c r="R12" t="n">
-        <v>7151180</v>
+        <v>7151153</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1781,17 +1780,13 @@
           <t>2025-10-28</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>ringhack på gammal gran</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1810,10 +1805,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129742521</v>
+        <v>129745347</v>
       </c>
       <c r="B13" t="n">
-        <v>57740</v>
+        <v>79089</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1821,31 +1816,30 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1853,10 +1847,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>789331</v>
+        <v>789248</v>
       </c>
       <c r="R13" t="n">
-        <v>7151248</v>
+        <v>7151191</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1893,7 +1887,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>ringhack på tall</t>
+          <t>på stammen av en tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1902,6 +1896,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1920,10 +1915,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129745950</v>
+        <v>129745328</v>
       </c>
       <c r="B14" t="n">
-        <v>82925</v>
+        <v>79089</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1931,27 +1926,27 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -1962,10 +1957,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>789199</v>
+        <v>789227</v>
       </c>
       <c r="R14" t="n">
-        <v>7151153</v>
+        <v>7151210</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2025,10 +2020,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129745347</v>
+        <v>129743913</v>
       </c>
       <c r="B15" t="n">
-        <v>79088</v>
+        <v>57740</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2036,30 +2031,31 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2067,10 +2063,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>789248</v>
+        <v>789283</v>
       </c>
       <c r="R15" t="n">
-        <v>7151191</v>
+        <v>7151180</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2107,7 +2103,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>på stammen av en tall</t>
+          <t>ringhack på gammal gran</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2116,7 +2112,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2135,10 +2130,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129745328</v>
+        <v>129742521</v>
       </c>
       <c r="B16" t="n">
-        <v>79088</v>
+        <v>57740</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2146,30 +2141,31 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2177,10 +2173,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>789227</v>
+        <v>789331</v>
       </c>
       <c r="R16" t="n">
-        <v>7151210</v>
+        <v>7151248</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2215,13 +2211,17 @@
           <t>2025-10-28</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>ringhack på tall</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2243,7 +2243,7 @@
         <v>129746089</v>
       </c>
       <c r="B17" t="n">
-        <v>82925</v>
+        <v>82931</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2345,10 +2345,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129742406</v>
+        <v>129745466</v>
       </c>
       <c r="B18" t="n">
-        <v>79088</v>
+        <v>57737</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2356,30 +2356,31 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2387,10 +2388,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>789267</v>
+        <v>789212</v>
       </c>
       <c r="R18" t="n">
-        <v>7151238</v>
+        <v>7151164</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2425,13 +2426,17 @@
           <t>2025-10-28</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>bohål i gran</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2450,10 +2455,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129745466</v>
+        <v>129742406</v>
       </c>
       <c r="B19" t="n">
-        <v>57737</v>
+        <v>79089</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2461,31 +2466,30 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2493,10 +2497,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>789212</v>
+        <v>789267</v>
       </c>
       <c r="R19" t="n">
-        <v>7151164</v>
+        <v>7151238</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2531,17 +2535,13 @@
           <t>2025-10-28</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>bohål i gran</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2672,10 +2672,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129742631</v>
+        <v>129745993</v>
       </c>
       <c r="B21" t="n">
-        <v>91557</v>
+        <v>79089</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2683,27 +2683,27 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>112</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -2714,10 +2714,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>789289</v>
+        <v>789196</v>
       </c>
       <c r="R21" t="n">
-        <v>7151198</v>
+        <v>7151151</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2750,6 +2750,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>ca 70cm lång bål!</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2777,10 +2782,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129745993</v>
+        <v>129742631</v>
       </c>
       <c r="B22" t="n">
-        <v>79088</v>
+        <v>91574</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2788,27 +2793,27 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>112</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -2819,10 +2824,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>789196</v>
+        <v>789289</v>
       </c>
       <c r="R22" t="n">
-        <v>7151151</v>
+        <v>7151198</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2855,11 +2860,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-28</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>ca 70cm lång bål!</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2890,7 +2890,7 @@
         <v>129745192</v>
       </c>
       <c r="B23" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2992,42 +2992,37 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129745532</v>
+        <v>129742557</v>
       </c>
       <c r="B24" t="n">
-        <v>57737</v>
+        <v>92076</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>1209</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3035,10 +3030,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>789215</v>
+        <v>789298</v>
       </c>
       <c r="R24" t="n">
-        <v>7151159</v>
+        <v>7151197</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3075,7 +3070,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>hack i låga</t>
+          <t>på samma granlåga som ullticka</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3084,6 +3079,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3102,37 +3098,42 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129742557</v>
+        <v>129745532</v>
       </c>
       <c r="B25" t="n">
-        <v>92059</v>
+        <v>57737</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1209</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3140,10 +3141,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>789298</v>
+        <v>789215</v>
       </c>
       <c r="R25" t="n">
-        <v>7151197</v>
+        <v>7151159</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3180,7 +3181,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>på samma granlåga som ullticka</t>
+          <t>hack i låga</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3189,7 +3190,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3208,41 +3208,42 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129745563</v>
+        <v>129744135</v>
       </c>
       <c r="B26" t="n">
-        <v>91570</v>
+        <v>57740</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3250,10 +3251,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>789198</v>
+        <v>789284</v>
       </c>
       <c r="R26" t="n">
-        <v>7151158</v>
+        <v>7151167</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3288,13 +3289,17 @@
           <t>2025-10-28</t>
         </is>
       </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>äldre ringhack på gran</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3313,42 +3318,41 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129744135</v>
+        <v>129745563</v>
       </c>
       <c r="B27" t="n">
-        <v>57740</v>
+        <v>91587</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3356,10 +3360,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>789284</v>
+        <v>789198</v>
       </c>
       <c r="R27" t="n">
-        <v>7151167</v>
+        <v>7151158</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3394,17 +3398,13 @@
           <t>2025-10-28</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>äldre ringhack på gran</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3426,7 +3426,7 @@
         <v>129745551</v>
       </c>
       <c r="B28" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3528,10 +3528,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129745383</v>
+        <v>129745427</v>
       </c>
       <c r="B29" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3562,11 +3562,7 @@
           <t>bålar</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3574,7 +3570,7 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>789239</v>
+        <v>789221</v>
       </c>
       <c r="R29" t="n">
         <v>7151169</v>
@@ -3610,11 +3606,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-10-28</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>fertil</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3642,38 +3633,38 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129745427</v>
+        <v>129742620</v>
       </c>
       <c r="B30" t="n">
-        <v>79088</v>
+        <v>91587</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
@@ -3684,10 +3675,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>789221</v>
+        <v>789294</v>
       </c>
       <c r="R30" t="n">
-        <v>7151169</v>
+        <v>7151188</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3747,41 +3738,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129742620</v>
+        <v>129745383</v>
       </c>
       <c r="B31" t="n">
-        <v>91570</v>
+        <v>79089</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr"/>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3789,10 +3784,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>789294</v>
+        <v>789239</v>
       </c>
       <c r="R31" t="n">
-        <v>7151188</v>
+        <v>7151169</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3825,6 +3820,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>fertil</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3852,10 +3852,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129745155</v>
+        <v>129742300</v>
       </c>
       <c r="B32" t="n">
-        <v>79088</v>
+        <v>57737</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3863,30 +3863,31 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -3894,10 +3895,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>789288</v>
+        <v>789197</v>
       </c>
       <c r="R32" t="n">
-        <v>7151234</v>
+        <v>7151175</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3932,13 +3933,17 @@
           <t>2025-10-28</t>
         </is>
       </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>hål i tall</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -3957,10 +3962,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129742300</v>
+        <v>129745155</v>
       </c>
       <c r="B33" t="n">
-        <v>57737</v>
+        <v>79089</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3968,31 +3973,30 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4000,10 +4004,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>789197</v>
+        <v>789288</v>
       </c>
       <c r="R33" t="n">
-        <v>7151175</v>
+        <v>7151234</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4038,17 +4042,13 @@
           <t>2025-10-28</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>hål i tall</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4070,7 +4070,7 @@
         <v>129742254</v>
       </c>
       <c r="B34" t="n">
-        <v>79120</v>
+        <v>79121</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4172,10 +4172,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129742261</v>
+        <v>129744558</v>
       </c>
       <c r="B35" t="n">
-        <v>57740</v>
+        <v>91623</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4183,27 +4183,30 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4211,10 +4214,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>789192</v>
+        <v>789368</v>
       </c>
       <c r="R35" t="n">
-        <v>7151225</v>
+        <v>7151214</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4249,17 +4252,13 @@
           <t>2025-10-28</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>barksprätt på gammal gran</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4278,10 +4277,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129744558</v>
+        <v>129742429</v>
       </c>
       <c r="B36" t="n">
-        <v>91606</v>
+        <v>79089</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4289,27 +4288,27 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
@@ -4320,10 +4319,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>789368</v>
+        <v>789351</v>
       </c>
       <c r="R36" t="n">
-        <v>7151214</v>
+        <v>7151276</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4383,10 +4382,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129742429</v>
+        <v>129742261</v>
       </c>
       <c r="B37" t="n">
-        <v>79088</v>
+        <v>57740</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4394,30 +4393,27 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4425,10 +4421,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>789351</v>
+        <v>789192</v>
       </c>
       <c r="R37" t="n">
-        <v>7151276</v>
+        <v>7151225</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4463,13 +4459,17 @@
           <t>2025-10-28</t>
         </is>
       </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>barksprätt på gammal gran</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4491,7 +4491,7 @@
         <v>129742447</v>
       </c>
       <c r="B38" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4601,7 +4601,7 @@
         <v>129745159</v>
       </c>
       <c r="B39" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4706,7 +4706,7 @@
         <v>129745167</v>
       </c>
       <c r="B40" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4811,7 +4811,7 @@
         <v>129745946</v>
       </c>
       <c r="B41" t="n">
-        <v>82925</v>
+        <v>82931</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4913,38 +4913,38 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129742516</v>
+        <v>129742518</v>
       </c>
       <c r="B42" t="n">
-        <v>79088</v>
+        <v>91587</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K42" t="inlineStr"/>
@@ -4955,10 +4955,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>789348</v>
+        <v>789345</v>
       </c>
       <c r="R42" t="n">
-        <v>7151255</v>
+        <v>7151261</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5018,38 +5018,38 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129742518</v>
+        <v>129742516</v>
       </c>
       <c r="B43" t="n">
-        <v>91570</v>
+        <v>79089</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K43" t="inlineStr"/>
@@ -5060,10 +5060,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>789345</v>
+        <v>789348</v>
       </c>
       <c r="R43" t="n">
-        <v>7151261</v>
+        <v>7151255</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>

--- a/artfynd/A 50406-2025 artfynd.xlsx
+++ b/artfynd/A 50406-2025 artfynd.xlsx
@@ -5126,7 +5126,7 @@
         <v>129825892</v>
       </c>
       <c r="B44" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>

--- a/artfynd/A 50406-2025 artfynd.xlsx
+++ b/artfynd/A 50406-2025 artfynd.xlsx
@@ -4258,7 +4258,7 @@
         <v>0</v>
       </c>
       <c r="AE35" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG35" t="b">
         <v>0</v>
@@ -5126,7 +5126,7 @@
         <v>129825892</v>
       </c>
       <c r="B44" t="n">
-        <v>57826</v>
+        <v>57741</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5213,7 +5213,7 @@
         <v>0</v>
       </c>
       <c r="AE44" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG44" t="b">
         <v>0</v>

--- a/artfynd/A 50406-2025 artfynd.xlsx
+++ b/artfynd/A 50406-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY54"/>
+  <dimension ref="A1:AZ54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129240151</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129742631</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -979,6 +994,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129742254</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129240149</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1186,6 +1211,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129742539</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1291,6 +1321,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129744558</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1388,6 +1423,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129240155</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1494,6 +1534,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129742557</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1599,6 +1644,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129745889</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1704,6 +1754,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129745946</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1809,6 +1864,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129745950</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1914,6 +1974,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129746089</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2011,6 +2076,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129240135</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2116,6 +2186,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129742518</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2221,6 +2296,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129742620</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2326,6 +2406,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129745563</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2423,6 +2508,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129240172</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2520,6 +2610,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129240173</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2625,6 +2720,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129742406</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2730,6 +2830,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129742429</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2840,6 +2945,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129742447</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2945,6 +3055,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129742487</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3050,6 +3165,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129742516</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3155,6 +3275,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129745155</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3260,6 +3385,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129745159</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3365,6 +3495,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129745167</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3470,6 +3605,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129745192</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3575,6 +3715,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129745328</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3685,6 +3830,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129745347</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3799,6 +3949,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129745383</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3904,6 +4059,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129745427</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4009,6 +4169,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129745551</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4119,6 +4284,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129745993</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4216,6 +4386,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129240153</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4326,6 +4501,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129742300</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4436,6 +4616,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129742984</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4546,6 +4731,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129745363</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4656,6 +4846,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129745466</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4766,6 +4961,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129745532</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4872,6 +5072,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129742261</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4982,6 +5187,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129742521</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5092,6 +5302,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129743137</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5202,6 +5417,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129743913</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5312,6 +5532,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129744135</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5422,6 +5647,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129744197</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5532,6 +5762,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129744349</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5642,6 +5877,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129744386</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5752,6 +5992,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129744422</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5862,6 +6107,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129744545</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5972,6 +6222,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129825302</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6082,6 +6337,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129825414</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6192,6 +6452,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129825892</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6304,8 +6569,68 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129742963</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>